--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$F$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1964,17 +1964,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.8 - History UI</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Dynamic axis labels (hours/days/dates) based on window</t>
+          <t>Backend: flows + flow_steps + flow_runs + step_results + variable_cache tables</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1984,29 +1984,29 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Activity Timeline auto-formats</t>
+          <t>SQLite schema with full FK relations</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>HTTP method support (GET/POST/PUT/PATCH)</t>
+          <t>Backend: extraction.ts with mini JSONPath + header + status capture</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2016,29 +2016,29 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>DELETE blocked for safety</t>
+          <t>Zero deps; supports $.foo.bar / arrays / quoted keys</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Body editor with type selector</t>
+          <t>Backend: variable substitution ({{name}} in URL/headers/body/params)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2048,29 +2048,29 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>JSON / form / urlencoded</t>
+          <t>Find-and-replace before sending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Custom headers tab (key-value editor)</t>
+          <t>Backend: flowRunner.ts - atomic execution + stop-on-failure + skip cascade</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2080,29 +2080,29 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Sent on every check</t>
+          <t>Industry standard atomic flow execution</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Query parameters tab (key-value editor)</t>
+          <t>Backend: smart caching with TTL (skip step if all vars still fresh)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2112,29 +2112,29 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Appended to URL automatically</t>
+          <t>Massive cost saver - don't re-login if token valid</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Assertions engine (4 v1 types)</t>
+          <t>Backend: per-step retries with exponential backoff</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2144,29 +2144,29 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>status equals / in range / latency under / body contains</t>
+          <t>Kills false alerts from network blips</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Assertion result pills on URL cards</t>
+          <t>Backend: custom wait between steps for async APIs</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -2176,29 +2176,29 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Green check / red X</t>
+          <t>POST job -&gt; wait 5s -&gt; poll status</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.9 - Postman parity</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Raw body type with custom Content-Type (Text/XML/HTML/JS/YAML/custom)</t>
+          <t>Backend: monitor scheduler extended to run due flows atomically</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -2208,29 +2208,29 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Postman raw mode equivalent</t>
+          <t>One interval per flow not per step</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Run Audit button (manual Check All)</t>
+          <t>Backend: Slack alert on flow failure (per-project webhook)</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2240,29 +2240,29 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Concurrency capped at 8 parallel</t>
+          <t>Reuses existing slack.ts</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>HTML report generator</t>
+          <t>Backend: 13 REST endpoints (flows/steps/runs/cache CRUD)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2272,29 +2272,29 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Standalone HTML in data/reports/</t>
+          <t>Full CRUD + reorder + manual trigger</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Slack Block Kit message format</t>
+          <t>Frontend: FlowEditor modal (name/interval/stop-on-failure)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2304,29 +2304,29 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Rich KPIs and failure details</t>
+          <t>Create + edit + enable/disable</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Slack file upload (HTML attached)</t>
+          <t>Frontend: StepEditor modal with 7 tabs (Basics/Params/Headers/Body/Assertions/Extract/Retry)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2336,29 +2336,29 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>@slack/web-api files.uploadV2</t>
+          <t>Full Postman parity + extractions + retries</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Audit progress modal + result modal</t>
+          <t>Frontend: Variables hint shows available {{vars}} from prior steps</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2368,57 +2368,61 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Spinner during run; summary after</t>
+          <t>Self-documenting flow editor</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.10 - Audit + Slack</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Get Slack Bot Token (xoxb-) and configure</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Frontend: FlowCard with expandable step list + per-step results</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>User: paste in Settings to enable Slack uploads</t>
+          <t>One run shown inline; click step to edit</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.11 - Discoverability</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Search by URL/description/method</t>
+          <t>Frontend: Run Now button with spinner + last-run timestamp</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2428,29 +2432,29 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Filters list live as you type</t>
+          <t>Manual trigger from UI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.11 - Discoverability</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Numbered pagination (LeetCode style)</t>
+          <t>Frontend: Flows section integrated above Standalone URLs in ProjectView</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -2460,29 +2464,29 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Smart ellipsis for many pages</t>
+          <t>Clean separation of flows vs independent URLs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.11 - Discoverability</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Method filter chips (color-coded)</t>
+          <t>UX: wrap Flows + URLs in visual section panels with header/count/actions</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2492,29 +2496,29 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>GET green / POST orange / PUT cyan / PATCH purple</t>
+          <t>Notion/Linear style - fixes orphaned search bar issue</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.11 - Discoverability</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Search bar with icon + keyboard shortcut (/)</t>
+          <t>UX: GitHub-style tab navigation (Standalone URLs / Flows) with count badges + active underline</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2524,29 +2528,29 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Press / anywhere to focus</t>
+          <t>Each tab has its own search/filters - scales to many items</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Phase 1.11 - Discoverability</t>
+          <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Result count chip in search</t>
+          <t>UX: URL hash persistence for tabs (#urls / #flows) + danger badge on failing count</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2556,205 +2560,1161 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Highlights blue when filter active</t>
+          <t>Refresh stays on same tab; bookmarkable; failures visible without switching</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>UX: switching projects in sidebar resets to URLs tab (deep-link still respected on refresh)</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Fixes confusing "I was on Flows in A; clicking B opens Flows in B too"</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>UX: tighten vertical rhythm (main gap 24px-&gt;12px) + breathing room before section panel</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Less visual clutter; rests where rests are needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Backend: Run Audit now includes flows (re-runs all enabled flows alongside URL checks)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Single button audits everything in project</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Backend: HTML report has dedicated Flows table section + 4 KPIs with breakdown</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>URLs section + Flows section + per-step status badges</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>13.24</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Backend: Slack Block Kit message split into URL track + Flow track</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Dual stats row + separate failing lists for each type</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>13.25</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Backend: store extends list queries with lastRunOk + lastRunTotalMs via correlated subquery</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Single SQL roundtrip - no N+1 issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>13.26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: KpiBar flow-aware (Endpoints label + breakdowns) with graceful no-flows fallback</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Single bar tells full story</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>13.27</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Audit result modal shows dual-track URL/Flow breakdown</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Clear separation in result feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>13.28</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Flows tab gets mini-KPI strip (Total/Healthy/Failing/Avg run/Last run)</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Flow-level health at a glance</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>13.29</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>UX: Flow KPI strip enlarged + tooltips on every cell + show which flow last ran</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Last run cell shows flow name as subtext; all cells hover-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>13.30</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.13 - Flows (API chaining)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Flow KPI strip auto-updates after Run Now (no page refresh needed)</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>FlowCard onAfterRun callback bumps a flows-refresh tick in ProjectView</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.8 - History UI</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic axis labels (hours/days/dates) based on window</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Activity Timeline auto-formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>HTTP method support (GET/POST/PUT/PATCH)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>DELETE blocked for safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Body editor with type selector</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>JSON / form / urlencoded</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Custom headers tab (key-value editor)</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Sent on every check</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Query parameters tab (key-value editor)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Appended to URL automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Assertions engine (4 v1 types)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>status equals / in range / latency under / body contains</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Assertion result pills on URL cards</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Green check / red X</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.9 - Postman parity</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Raw body type with custom Content-Type (Text/XML/HTML/JS/YAML/custom)</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Postman raw mode equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Run Audit button (manual Check All)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Concurrency capped at 8 parallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>HTML report generator</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Standalone HTML in data/reports/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Slack Block Kit message format</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Rich KPIs and failure details</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Slack file upload (HTML attached)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>@slack/web-api files.uploadV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Audit progress modal + result modal</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Spinner during run; summary after</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.10 - Audit + Slack</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Get Slack Bot Token (xoxb-) and configure</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>User: paste in Settings to enable Slack uploads</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.11 - Discoverability</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Search by URL/description/method</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Filters list live as you type</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.11 - Discoverability</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Numbered pagination (LeetCode style)</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Smart ellipsis for many pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.11 - Discoverability</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Method filter chips (color-coded)</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>GET green / POST orange / PUT cyan / PATCH purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.11 - Discoverability</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Search bar with icon + keyboard shortcut (/)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Press / anywhere to focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.11 - Discoverability</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Result count chip in search</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Highlights blue when filter active</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>New URLs appear at top of list</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>ORDER BY rowid DESC</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Demo: API key with/without (httpbin/bearer)</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>Showed 401 vs 200 with same URL</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Demo: Basic Auth with httpbin/basic-auth</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>Different auth style demonstrated</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Demo: POST + JSON body to httpbin/post</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>Confirmed body sent correctly</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Explanation doc: how Phase 1 connects to Phase 2</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>Mapped each Phase 2 requirement to Phase 1 file</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Manager meeting: present plan and get approval</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>User to schedule</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
+  <autoFilter ref="A1:F101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$F$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3713,8 +3713,993 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Backend: 4 new tables (prereq_steps / prereq_runs / prereq_step_results / project_variable_cache) + project columns</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Project-level setup chain + variable pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Backend: store CRUD + run lifecycle + project-pool variable cache</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>listPrereqSteps / startPrereqRun / cacheProjectVariable etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Backend: prereqRunner.ts (sequential exec</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> retries</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wait</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TTL</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> captures to project pool)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors flowRunner with project-scoped persistence</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Backend: monitor.ts substitutes project-pool {{vars}} into every standalone URL check</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>URL custom headers and body now resolve {{auth_token}} etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Backend: flowRunner.ts merges project pool + flow cache (flow-scoped wins on conflict)</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Hierarchical variable scoping (project &lt; flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Backend: monitor tick auto-runs due prereq chains (before URLs/flows)</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Tokens stay warm without manual refresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Backend: REST endpoints (CRUD prereq steps / run / list runs / get vars / clear vars)</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>7 new routes wired in index.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: PrereqsPanel — collapsible panel above tab nav with status header + Run Now</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Visible on both URLs and Flows tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: PrereqStepEditorForm (shares 7-tab UX with FlowStep editor)</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Reuses BodyEditor / AssertionsEditor / ExtractionsEditor / RetryWaitEditor</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>14.10</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Variables hint in Flow step editor now includes prereq-chain vars</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Surfaced via projectVars prop loaded by App</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: live project variable list (with TTL countdown) + Clear vars button</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Renders captured pool inline in the panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>14.12</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: per-project schedule controls (interval + enable/disable)</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Saves via PATCH /projects/:id with new fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>14.13</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: prereq captures token + URL substitutes it + body-contains assertion passes</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end substitution proven via httpbin /post → /headers</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>14.14</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Backend: {{var}} substitution inside assertion config (body-contains text)</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Closes the brittleness gap — assertions tracking rotating session/auth tokens stay green</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>14.15</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Backend: evaluateAssertions accepts vars param + 3 callsites wire it through (monitor / flowRunner / prereqRunner)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Single source of truth - same vars used for substitution everywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>14.16</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: assertion UI hints {{var}} support (placeholder + tip line)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Users discover the feature without docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: prereq re-run after pool clear keeps flow green automatically</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Proven across 3 step shapes (body / header / query param) on Default project</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>14.18</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Backend: split runners into kickoff (sync runId) + executeRun (background); new /run-async endpoints return 202 with runId</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Frontend can now show live per-step progress instead of a blocking spinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: FlowCard + PrereqsPanel poll runId every 500ms; render running-pulse pill / queued dashed pill / progress bar</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Step state transitions queued &gt; running &gt; done in real time</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>14.20</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UX: progress bar shows 'Step N of M running...' + completed count above step list</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Replaces 'simply loading n loading' opaque spinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>14.21</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Backend: force flag on kickoff functions bypasses smart TTL skip-cache; /run-async accepts ?force=true</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Production-grade pattern - human clicks bypass caches</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> scheduler keeps them</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>14.22</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: manual Run-now buttons always pass force=true (FlowCard + PrereqsPanel)</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Button now does what it says - no more confusing SKIPPED on click</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>14.23</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.14 - Prerequisites</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: scheduler skips when fresh / manual click always refreshes the pool</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Verified pool value before/after to prove both paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Active project persists across page refresh (localStorage)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Refresh keeps you where you were instead of dumping to default</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Per-project scroll memory: save on leave / restore on return / top on fresh</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Switching projects no longer 'inherits' middle-of-page scroll from the previous one</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Prereq panel auto-collapses 1.5s after run completes (restores pre-click state)</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Expands during run for live progress then snaps back as if untouched</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Two-click inline confirm for step delete (replaces native window.confirm)</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Avoids ugly browser confirm modal nested inside our editor modal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Document title reflects active project + failing count</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Tab title now '(3 failing) Project Name - Functional Monitor'</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Sidebar shows failing-count badge per project (pulsing red)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Spot failing projects at a glance without clicking each one</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Step rows truncate long URLs cleanly (ellipsis + monospace)</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Prevents long URLs from pushing the edit hint off the card</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F101"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4698,8 +4698,168 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Backend: liveStep map in flowRunner + prereqRunner; each retry attempt + backoff phase is published in-memory</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Enables live retry visibility without DB writes per attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Backend: GET /flow-runs/:id and /prereq-runs/:id enrich response with optional liveStep while run is mid-flight</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Single endpoint - existing poll cadence picks it up</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>15.10</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: running step pill switches to amber "RETRY N/M" + step row tints amber during retries</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Distinguishes a retry-in-progress from a fresh attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: progress bar shows "retry N of M (waiting before next try)" + last-try status code chip</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>No more silent waits during exponential backoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>15.12</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.15 - UX hardening</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: 503 endpoint with 3 retries traces attempt 1 to 4 transitions including backoff phase</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Verified via /api/flow-runs/:id polling at 350ms cadence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4858,8 +4858,616 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Backend: uploads table + on-disk storage in data/uploads/&lt;uuid&gt;</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>One row per file; bytes live on disk not in SQLite</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Backend: paths.ts helper centralises UPLOADS_DIR + per-id path</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Shared by index.ts upload routes and timing.ts body builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Backend: POST/GET/DELETE routes (express.raw 10MB cap; URL-encoded x-filename header)</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>No multer dependency; raw bytes go straight to disk</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Backend: store CRUD (createUpload/getUpload/listUploadsByProject/deleteUpload)</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors existing row-mapper pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Backend: bodyType=binary in timing.ts parses {uploadId fieldName?} body and builds raw or multipart</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Empty fieldName = raw bytes; set = multipart/form-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: shared BinaryBodyEditor with file picker / image preview / field-name / existing-uploads picker</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Single component reused by URL + Flow step + Prereq step editors</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Binary tab added to all three body editors (URL form / Flow step / Prereq step)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Discoverable in same Body tab as JSON / Raw / form-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UX: Run Now on a Flow auto-runs the prereq chain first with force=true</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Avoids spurious failures from stale auth tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UX: Audit renamed Generate report - snapshots current state; ?refresh=true opt-in for re-check</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Used to re-run everything; now defaults to fast snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>16.10</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: upload list readback delete round-trip via curl</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Verified POST returns id; GET streams bytes; DELETE 204s</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>16.11</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: BinaryBodyEditor redesigned as full dropzone (click or drag-drop) with hover/dragover states</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Old "Upload file" button was ambiguous - users were unsure whether click would open picker or upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>16.12</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: real upload progress bar (XHR onprogress with %) replaces opaque "Uploading..." text</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Live feedback for large files; no more guessing if it hung</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: client-side max-size guard (10MB) shows inline error before hitting server</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Saves a wasted upload + slow round-trip for over-cap files</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>16.14</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: selected file card with thumb / ext badge / size / inline replace+delete actions</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Replaces compact row that buried the actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>16.15</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: explicit Raw vs Form-field radio toggle (vs cryptic empty-fieldname meaning)</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Beginners no longer have to read help text to understand what empty fieldname does</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: success+error banners with auto-dismiss (3s) after upload completes or fails</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Confirms upload succeeded without forcing scroll to bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>16.17</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: project upload library collapsed by default (toggle to expand)</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Cleaner default view when project has many uploads</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>16.18</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Flow card surfaces "Refreshing access tokens..." banner during prereq phase</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Previously only a PREREQ pill switch - banner makes the wait self-explanatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>16.19</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: Audit button copy "Snapshot &amp; report" + tooltip clarifies no re-checks happen</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Button now reads as the action it performs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J136"/>
+  <autoFilter ref="A1:J155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -5191,7 +5191,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Frontend: BinaryBodyEditor redesigned as full dropzone (click or drag-drop) with hover/dragover states</t>
+          <t>Frontend: BinaryBodyEditor rebuilt in Postman style - Select File button + inline filename + clear x; compact utilitarian row</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Old "Upload file" button was ambiguous - users were unsure whether click would open picker or upload</t>
+          <t>User feedback: oversized dropzone felt out of place vs rest of Postman-like editor</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Frontend: selected file card with thumb / ext badge / size / inline replace+delete actions</t>
+          <t>Frontend: inline filename + size display with x clear button (Postman binary tab layout)</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Replaces compact row that buried the actions</t>
+          <t>Matches Postman binary body editor exactly</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Frontend: explicit Raw vs Form-field radio toggle (vs cryptic empty-fieldname meaning)</t>
+          <t>Frontend: Field name (optional) inline input - empty = raw bytes / set = multipart</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Beginners no longer have to read help text to understand what empty fieldname does</t>
+          <t>Postman-style single-tab semantic instead of radio toggle</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Frontend: success+error banners with auto-dismiss (3s) after upload completes or fails</t>
+          <t>Frontend: inline left-bar error message (no large banners)</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Confirms upload succeeded without forcing scroll to bottom</t>
+          <t>Postman-style subdued inline feedback</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Frontend: project upload library collapsed by default (toggle to expand)</t>
+          <t>Frontend: project uploads library - collapsible tight rows with thumb/ext / check for active / hover-only delete</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Cleaner default view when project has many uploads</t>
+          <t>Postman-style tight row list</t>
         </is>
       </c>
     </row>

--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5466,8 +5466,40 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Fix: x button on selected file now deletes from project (not just unbinds from step)</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>User reported: deleted file still appeared in Project uploads list</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J155"/>
+  <autoFilter ref="A1:J156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5498,8 +5498,40 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Replace native window.confirm for upload delete with two-click inline confirm (matches existing step-delete pattern from 15.4)</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Stays in-app instead of jumping to browser modal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J156"/>
+  <autoFilter ref="A1:J157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5530,8 +5530,40 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>16.22</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Prereq banner now shows live step-N-of-M + completed count + retry chip + filling progress bar</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Previously opaque - users couldn't tell if prereq was progressing or stuck</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J157"/>
+  <autoFilter ref="A1:J158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5562,8 +5562,40 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>16.23</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.16 - Binary uploads + UX tightening</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>FlowCard Run-now lifts prereq runId up so PrereqsPanel attaches and shows the full step-by-step progress UI (matching panel's own Run-now behaviour)</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>User feedback: panel's complete bar only appeared when prereq triggered from the panel itself</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J158"/>
+  <autoFilter ref="A1:J159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5594,8 +5594,424 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Backend: copyFlowStepToFlow + moveFlowStepToFlow store fns (transactional / target positions shifted +1 / insert at pos=1 / source rebalanced on move)</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Single tx() per operation - no partial state on failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Backend: POST /api/steps/:id/copy-to-flow + /move-to-flow routes (400 on missing step / same flow / missing target)</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Reuses existing getFlow + getFlowStep guards</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: reorderPrereqSteps + copyStepToFlow + moveStepToFlow API wrappers</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors existing reorderFlowSteps pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: utils/varRefs.ts helper - findVarRefs + checkStepVarRefs scans url/body/headers/query for {{name}} tokens</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Reusable across Flow steps + Prereq steps via union type</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: arrow-up/down micro-stack column on every step row (FlowCard + PrereqsPanel) with first/last disabled + optimistic UI + disabled mid-run</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Manager chose arrow buttons over drag-and-drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: hover-revealed Move + Copy buttons on Flow step rows (not prereqs) - opens MoveCopyStepModal</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Scope is flow-to-flow only per design</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: MoveCopyStepModal lists other flows in project / empty-state row / confirm-row with Move-arrow or Copy-arrow primary button</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Drop position is always step 1 of target (no position picker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Frontend: warn chip on rows with broken {{var}} refs after reorder (non-blocking - runtime still attempts and surfaces real error)</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Allow + warn per design - never blocks user</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Smoke test: copy + move + reorder routes verified via curl on Default project (positions rebalanced correctly on both sides)</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Edges tested: same-flow 400 / missing step 400 / missing targetFlowId 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Move/Copy target flow now auto-refreshes (ProjectView combines flowsTick into the refreshTick passed to FlowCards)</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>User-reported: target flow didn't update until manual reload</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Fix: deleteFlowStep + deletePrereqStep rebalance positions inside tx() so 1/2/3 -&gt; 1/2 after deleting position 2</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>User-reported: numbers stayed sparse (1/3) after deletion</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>17.12</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Scroll position survives page reload via localStorage (fm:scroll:&lt;projectId&gt;) + beforeunload/pagehide/visibilitychange + double-rAF restore on first snapshot</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>User requested - was in-memory only before</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>17.13</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.17 - Step orchestration</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Per-project section memory: switching back to a project restores the last-viewed tab (#urls vs #flows) instead of forcing #urls; mirrored to localStorage on switch + page-hide</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>User-reported: switching projects was always resetting to #urls even on return visit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J159"/>
+  <autoFilter ref="A1:J172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$172</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,15 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0010B981"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009CA3AF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -50,21 +39,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
+        <fgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00D4EFDF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00FCF3CF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,46 +61,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E7EB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,15 +444,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3558,156 +3524,156 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Demo: API key with/without (httpbin/bearer)</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Showed 401 vs 200 with same URL</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Demo: Basic Auth with httpbin/basic-auth</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Different auth style demonstrated</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Demo: POST + JSON body to httpbin/post</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Confirmed body sent correctly</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Explanation doc: how Phase 1 connects to Phase 2</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Mapped each Phase 2 requirement to Phase 1 file</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Manager meeting: present plan and get approval</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr"/>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>User to schedule</t>
         </is>
@@ -6010,8 +5976,588 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Backend types.ts: new ForEachConfig interface + forEach field on FlowStep</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Single-level only - one for-each per flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Backend types.ts: iterationIndex + iterationCount on StepResult; forEachIteration + forEachTotal on LiveStepProgress</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Same iterationCount across every row of one iteration set</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Backend extraction.ts: jsonPath learns [*] wildcard (recursive flatten); ExtractedValue.value widened to string | unknown[]</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>$.data[*] returns whole array; $.data[*].id returns array of ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Backend extraction.ts: substitute learns dotted-path lookup (walks object-typed vars for {{student.id}})</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Bridges per-iteration item objects to template syntax</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Backend db.ts: idempotent ensureColumn migrations - for_each_config_json on flow_steps + iteration_index + iteration_count on step_results</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Existing rows default NULL = non-iterating step</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Backend store.ts: normalizeForEach (identifier validation) + assertSingleForEach (single-level guard) + serialize/parse in add/update/copy/move</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>400 with 'only one for-each step is allowed per flow' on guard violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Backend store.ts: recordStepResult writes iterationIndex/iterationCount; rowToFlowStep + rowToStepResult parse them back</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Prereq runner passes nulls (prereqs never iterate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: iteration fork - resolves array var / caps at 100 / loops with per-iteration vars / records per-iteration row / never stops flow on iter failure</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Failure policy locked by user constraint #1 - continue all iterations</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: LiveStepProgress publishes forEachIteration + forEachTotal between iterations</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Mid-flight UI gets 'iteration X of N' label</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>18.10</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts + assertions.ts + prereqRunner.ts: widen vars map to Record&lt;string</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>unknown&gt; with stringify on persistence</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Bridges array/object vars in-memory vs string-only DB rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Frontend types.ts: mirror backend - ForEachConfig + forEach on FlowStep + iteration* on StepResult + forEach* on LiveStepProgress</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Single source-of-truth alignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>18.12</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Frontend flowForms.tsx: new For each tab with dropdown of array-typed vars + item-name input + Disable button + single-level warning banner</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Candidates auto-derived from earlier steps' extractions that use [*]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>18.13</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: arrow-cycle pill 'for each {{item}}' in step header next to method tag</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Indigo tint - subtle but discoverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>18.14</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: (N) check X / cross Y summary chip + chevron toggles scrollable per-iteration panel (status + latency + error reason + retry count)</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Max-height 260px - doesn't render 100 inline rows per user constraint #3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: live progress label gets 'iteration X of N' suffix when liveStep.forEachTotal set</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Increments per iteration; complements existing Step N of M label</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Frontend varRefs.ts: regex widened to recognise {{name.dotted.path}}; checkStepVarRefs adds loop-local itemVarName to known set</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>No false-warn for {{student.id}} inside a for-each step</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>18.17</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: .step-foreach-pill (indigo) + .step-iterations-summary (green/red w/ chevron) + .step-iterations-panel + .step-foreach-warning (yellow)</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Visual weight matches existing extract-row editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.18 - For-each step</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Build clean: tsc -b on backend + tsc -b + vite build on frontend</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Zero warnings; production bundle 273KB JS / 58KB CSS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,17 +39,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EFDF"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCF3CF"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,20 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -488,6072 +481,6296 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Backend project setup (Node.js + TypeScript + Express)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>tsx watch dev server</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Frontend project setup (React + Vite + TypeScript)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Vite dev server with proxy to backend</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Implement URL ingestion endpoint (POST /api/urls)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Add and remove URLs via REST</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Implement status checker (HTTP GET to URL)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Captures HTTP status code</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Group URLs by status family (2xx/3xx/4xx/5xx/error)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>classify() pure function</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Frontend dashboard with grouped count cards</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>React + CSS color-coded</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Real-time refresh (frontend polls every 3s)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>setInterval + useEffect</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>JSON file persistence with atomic writes</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>data/db.json with .tmp + rename</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Project segregation (multiple projects + sidebar)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Each project = monitored service</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Per-project API key vault</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Configurable header name + prefix</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Auth header injection for monitored URLs</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Bearer / x-api-key / Basic supported</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Per-URL configurable check interval</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Default 5 min; range 1-1440</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>5-phase HTTP latency tracking</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>DNS / TCP / TLS / TTFB / Download via raw https</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Description field per URL</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Free-text endpoint label</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Error reason mapping (human-readable)</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>DNS fail / cert expired / 401 / 503 etc</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Slack webhook integration for failure alerts</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Auto-fire on transition to failing</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Latency bar visualization (per-check breakdown)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Color-coded segments per phase</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Modal/dialog system (replace browser prompts)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Reusable Modal + ConfirmDialog</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Toast notifications (success / error feedback)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Auto-dismiss after 3.5s</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Design token system (spacing / type / radius / motion)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>CSS custom properties</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Polished sidebar with project avatars + health dots</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Color-hashed initials</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Animated transitions and hover states</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Cards lift; modals slide-up</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Migrate from JSON file to SQLite (node:sqlite)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Built-in - no native compile</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Schema design (projects/keys/urls/checks tables)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Foreign keys + indexes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Auto-migrate existing db.json to SQLite</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Old file backed up as .migrated.bak</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Persistent check history (every check stored)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>checks table with timestamps</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>7-day retention policy with auto-pruning</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Hourly cleanup job</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Extend retention to 365 days for long-range views</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Was 7 days; now keeps a year</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Sparkline component (24h latency trend)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Pure SVG no library</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Status strip (24h commit-graph style)</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Replaced by Activity Timeline (5.7)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Failure rate chip (color-coded by severity)</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Green &lt;1% / Amber 1-5% / Red &gt;5%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>KPI bar (4 KPIs + project sparkline)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Total / Healthy% / Avg latency / Failing</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>/api/urls/:id/history endpoint</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Returns checks since timestamp</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>/api/urls/:id/stats endpoint</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Total / failures / avg / p99</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Activity Timeline (unified history viz)</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Replaces status strip + sparkline</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Time Range Selector (24h/7d/30d/90d/1y/Custom) - LinkedIn style</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Re-renders all charts based on selection</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>5.10</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Time Range Selector visual redesign (segmented pill + sliding indicator)</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Datadog/Linear-inspired premium look</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Skeleton loaders on first paint</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Shimmer placeholders before /api/status arrives</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>12.2</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Spinner component + busy state in async buttons</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Replaces text-only Checking... state</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Toast notifications with success/error/info icons</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>SVG icons + colored borders</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Pulse animation on failing/degraded health dots in sidebar</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Calls attention to broken services</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Staggered fade+slide entrance for URL cards</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>40ms stagger between cards</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Smooth transitions on status pills + KPIs + chips</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>No more abrupt color/value snaps</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Consistent focus-visible rings across interactive elements</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Keyboard navigation accessibility</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Reduced-motion media query (a11y)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Respects prefers-reduced-motion</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Backend: flows + flow_steps + flow_runs + step_results + variable_cache tables</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>SQLite schema with full FK relations</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>13.2</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Backend: extraction.ts with mini JSONPath + header + status capture</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Zero deps; supports $.foo.bar / arrays / quoted keys</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Backend: variable substitution ({{name}} in URL/headers/body/params)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Find-and-replace before sending</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Backend: flowRunner.ts - atomic execution + stop-on-failure + skip cascade</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Industry standard atomic flow execution</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Backend: smart caching with TTL (skip step if all vars still fresh)</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Massive cost saver - don't re-login if token valid</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>13.6</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Backend: per-step retries with exponential backoff</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Kills false alerts from network blips</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Backend: custom wait between steps for async APIs</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>POST job -&gt; wait 5s -&gt; poll status</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>13.8</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Backend: monitor scheduler extended to run due flows atomically</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>One interval per flow not per step</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Backend: Slack alert on flow failure (per-project webhook)</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Reuses existing slack.ts</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>13.10</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Backend: 13 REST endpoints (flows/steps/runs/cache CRUD)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Full CRUD + reorder + manual trigger</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Frontend: FlowEditor modal (name/interval/stop-on-failure)</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Create + edit + enable/disable</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>13.12</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Frontend: StepEditor modal with 7 tabs (Basics/Params/Headers/Body/Assertions/Extract/Retry)</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Full Postman parity + extractions + retries</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>13.13</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Frontend: Variables hint shows available {{vars}} from prior steps</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Self-documenting flow editor</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>13.14</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Frontend: FlowCard with expandable step list + per-step results</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>One run shown inline; click step to edit</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>13.15</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Frontend: Run Now button with spinner + last-run timestamp</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Manual trigger from UI</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>13.16</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Frontend: Flows section integrated above Standalone URLs in ProjectView</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Clean separation of flows vs independent URLs</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>13.17</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>UX: wrap Flows + URLs in visual section panels with header/count/actions</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Notion/Linear style - fixes orphaned search bar issue</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>13.18</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>UX: GitHub-style tab navigation (Standalone URLs / Flows) with count badges + active underline</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Each tab has its own search/filters - scales to many items</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>13.19</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>UX: URL hash persistence for tabs (#urls / #flows) + danger badge on failing count</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Refresh stays on same tab; bookmarkable; failures visible without switching</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>13.20</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>UX: switching projects in sidebar resets to URLs tab (deep-link still respected on refresh)</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Fixes confusing "I was on Flows in A; clicking B opens Flows in B too"</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>13.21</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>UX: tighten vertical rhythm (main gap 24px-&gt;12px) + breathing room before section panel</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Less visual clutter; rests where rests are needed</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>13.22</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Backend: Run Audit now includes flows (re-runs all enabled flows alongside URL checks)</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Single button audits everything in project</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>13.23</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Backend: HTML report has dedicated Flows table section + 4 KPIs with breakdown</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>URLs section + Flows section + per-step status badges</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>13.24</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Backend: Slack Block Kit message split into URL track + Flow track</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Dual stats row + separate failing lists for each type</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>13.25</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Backend: store extends list queries with lastRunOk + lastRunTotalMs via correlated subquery</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Single SQL roundtrip - no N+1 issue</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>13.26</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Frontend: KpiBar flow-aware (Endpoints label + breakdowns) with graceful no-flows fallback</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Single bar tells full story</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>13.27</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Frontend: Audit result modal shows dual-track URL/Flow breakdown</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Clear separation in result feedback</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>13.28</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Frontend: Flows tab gets mini-KPI strip (Total/Healthy/Failing/Avg run/Last run)</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Flow-level health at a glance</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>13.29</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>UX: Flow KPI strip enlarged + tooltips on every cell + show which flow last ran</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Last run cell shows flow name as subtext; all cells hover-explained</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>13.30</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Fix: Flow KPI strip auto-updates after Run Now (no page refresh needed)</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>FlowCard onAfterRun callback bumps a flows-refresh tick in ProjectView</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Dynamic axis labels (hours/days/dates) based on window</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Activity Timeline auto-formats</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>HTTP method support (GET/POST/PUT/PATCH)</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>DELETE blocked for safety</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Body editor with type selector</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>JSON / form / urlencoded</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Custom headers tab (key-value editor)</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Sent on every check</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Query parameters tab (key-value editor)</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Appended to URL automatically</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Assertions engine (4 v1 types)</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>status equals / in range / latency under / body contains</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Assertion result pills on URL cards</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Green check / red X</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Raw body type with custom Content-Type (Text/XML/HTML/JS/YAML/custom)</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Postman raw mode equivalent</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Run Audit button (manual Check All)</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Concurrency capped at 8 parallel</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>HTML report generator</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Standalone HTML in data/reports/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Slack Block Kit message format</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Rich KPIs and failure details</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Slack file upload (HTML attached)</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>@slack/web-api files.uploadV2</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Audit progress modal + result modal</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Spinner during run; summary after</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Get Slack Bot Token (xoxb-) and configure</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
         <is>
           <t>User: paste in Settings to enable Slack uploads</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Search by URL/description/method</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Filters list live as you type</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Numbered pagination (LeetCode style)</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Smart ellipsis for many pages</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Method filter chips (color-coded)</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>GET green / POST orange / PUT cyan / PATCH purple</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Search bar with icon + keyboard shortcut (/)</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Press / anywhere to focus</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Result count chip in search</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Highlights blue when filter active</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>New URLs appear at top of list</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>ORDER BY rowid DESC</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Demo: API key with/without (httpbin/bearer)</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Showed 401 vs 200 with same URL</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Demo: Basic Auth with httpbin/basic-auth</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Different auth style demonstrated</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Demo: POST + JSON body to httpbin/post</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Confirmed body sent correctly</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Explanation doc: how Phase 1 connects to Phase 2</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Mapped each Phase 2 requirement to Phase 1 file</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Manager meeting: present plan and get approval</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
         <is>
           <t>User to schedule</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>14.1</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Backend: 4 new tables (prereq_steps / prereq_runs / prereq_step_results / project_variable_cache) + project columns</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Project-level setup chain + variable pool</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Backend: store CRUD + run lifecycle + project-pool variable cache</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>listPrereqSteps / startPrereqRun / cacheProjectVariable etc.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Backend: prereqRunner.ts (sequential exec</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t xml:space="preserve"> retries</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t xml:space="preserve"> wait</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t xml:space="preserve"> TTL</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve"> captures to project pool)</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Mirrors flowRunner with project-scoped persistence</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Backend: monitor.ts substitutes project-pool {{vars}} into every standalone URL check</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>URL custom headers and body now resolve {{auth_token}} etc.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Backend: flowRunner.ts merges project pool + flow cache (flow-scoped wins on conflict)</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Hierarchical variable scoping (project &lt; flow)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>14.6</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Backend: monitor tick auto-runs due prereq chains (before URLs/flows)</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Tokens stay warm without manual refresh</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Backend: REST endpoints (CRUD prereq steps / run / list runs / get vars / clear vars)</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>7 new routes wired in index.ts</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>14.8</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Frontend: PrereqsPanel — collapsible panel above tab nav with status header + Run Now</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Visible on both URLs and Flows tabs</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Frontend: PrereqStepEditorForm (shares 7-tab UX with FlowStep editor)</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Reuses BodyEditor / AssertionsEditor / ExtractionsEditor / RetryWaitEditor</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>14.10</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Frontend: Variables hint in Flow step editor now includes prereq-chain vars</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Surfaced via projectVars prop loaded by App</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Frontend: live project variable list (with TTL countdown) + Clear vars button</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Renders captured pool inline in the panel</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>14.12</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Frontend: per-project schedule controls (interval + enable/disable)</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Saves via PATCH /projects/:id with new fields</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>14.13</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Smoke test: prereq captures token + URL substitutes it + body-contains assertion passes</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>End-to-end substitution proven via httpbin /post → /headers</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>14.14</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Backend: {{var}} substitution inside assertion config (body-contains text)</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Closes the brittleness gap — assertions tracking rotating session/auth tokens stay green</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>14.15</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Backend: evaluateAssertions accepts vars param + 3 callsites wire it through (monitor / flowRunner / prereqRunner)</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Single source of truth - same vars used for substitution everywhere</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>14.16</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Frontend: assertion UI hints {{var}} support (placeholder + tip line)</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Users discover the feature without docs</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>14.17</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Smoke test: prereq re-run after pool clear keeps flow green automatically</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Proven across 3 step shapes (body / header / query param) on Default project</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>14.18</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Backend: split runners into kickoff (sync runId) + executeRun (background); new /run-async endpoints return 202 with runId</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Frontend can now show live per-step progress instead of a blocking spinner</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>14.19</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Frontend: FlowCard + PrereqsPanel poll runId every 500ms; render running-pulse pill / queued dashed pill / progress bar</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Step state transitions queued &gt; running &gt; done in real time</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>14.20</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>UX: progress bar shows 'Step N of M running...' + completed count above step list</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Replaces 'simply loading n loading' opaque spinner</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>14.21</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Backend: force flag on kickoff functions bypasses smart TTL skip-cache; /run-async accepts ?force=true</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Production-grade pattern - human clicks bypass caches</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve"> scheduler keeps them</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>14.22</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Frontend: manual Run-now buttons always pass force=true (FlowCard + PrereqsPanel)</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Button now does what it says - no more confusing SKIPPED on click</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>14.23</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Smoke test: scheduler skips when fresh / manual click always refreshes the pool</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Verified pool value before/after to prove both paths</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Active project persists across page refresh (localStorage)</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Refresh keeps you where you were instead of dumping to default</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>15.2</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Per-project scroll memory: save on leave / restore on return / top on fresh</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Switching projects no longer 'inherits' middle-of-page scroll from the previous one</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Prereq panel auto-collapses 1.5s after run completes (restores pre-click state)</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Expands during run for live progress then snaps back as if untouched</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Two-click inline confirm for step delete (replaces native window.confirm)</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Avoids ugly browser confirm modal nested inside our editor modal</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>15.5</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Document title reflects active project + failing count</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Tab title now '(3 failing) Project Name - Functional Monitor'</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>15.6</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Sidebar shows failing-count badge per project (pulsing red)</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Spot failing projects at a glance without clicking each one</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Step rows truncate long URLs cleanly (ellipsis + monospace)</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Prevents long URLs from pushing the edit hint off the card</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Backend: liveStep map in flowRunner + prereqRunner; each retry attempt + backoff phase is published in-memory</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Enables live retry visibility without DB writes per attempt</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>15.9</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Backend: GET /flow-runs/:id and /prereq-runs/:id enrich response with optional liveStep while run is mid-flight</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Single endpoint - existing poll cadence picks it up</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>15.10</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Frontend: running step pill switches to amber "RETRY N/M" + step row tints amber during retries</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Distinguishes a retry-in-progress from a fresh attempt</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>15.11</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Frontend: progress bar shows "retry N of M (waiting before next try)" + last-try status code chip</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>No more silent waits during exponential backoff</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>15.12</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Smoke test: 503 endpoint with 3 retries traces attempt 1 to 4 transitions including backoff phase</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Verified via /api/flow-runs/:id polling at 350ms cadence</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Backend: uploads table + on-disk storage in data/uploads/&lt;uuid&gt;</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>One row per file; bytes live on disk not in SQLite</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Backend: paths.ts helper centralises UPLOADS_DIR + per-id path</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Shared by index.ts upload routes and timing.ts body builder</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>16.3</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Backend: POST/GET/DELETE routes (express.raw 10MB cap; URL-encoded x-filename header)</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>No multer dependency; raw bytes go straight to disk</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>16.4</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Backend: store CRUD (createUpload/getUpload/listUploadsByProject/deleteUpload)</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Mirrors existing row-mapper pattern</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Backend: bodyType=binary in timing.ts parses {uploadId fieldName?} body and builds raw or multipart</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Empty fieldName = raw bytes; set = multipart/form-data</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Frontend: shared BinaryBodyEditor with file picker / image preview / field-name / existing-uploads picker</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Single component reused by URL + Flow step + Prereq step editors</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>16.7</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Frontend: Binary tab added to all three body editors (URL form / Flow step / Prereq step)</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Discoverable in same Body tab as JSON / Raw / form-data</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>UX: Run Now on a Flow auto-runs the prereq chain first with force=true</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Avoids spurious failures from stale auth tokens</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>UX: Audit renamed Generate report - snapshots current state; ?refresh=true opt-in for re-check</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Used to re-run everything; now defaults to fast snapshot</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Smoke test: upload list readback delete round-trip via curl</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Verified POST returns id; GET streams bytes; DELETE 204s</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>16.11</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Frontend: BinaryBodyEditor rebuilt in Postman style - Select File button + inline filename + clear x; compact utilitarian row</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>User feedback: oversized dropzone felt out of place vs rest of Postman-like editor</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>16.12</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Frontend: real upload progress bar (XHR onprogress with %) replaces opaque "Uploading..." text</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Live feedback for large files; no more guessing if it hung</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>16.13</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Frontend: client-side max-size guard (10MB) shows inline error before hitting server</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Saves a wasted upload + slow round-trip for over-cap files</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>16.14</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Frontend: inline filename + size display with x clear button (Postman binary tab layout)</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Matches Postman binary body editor exactly</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>16.15</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Frontend: Field name (optional) inline input - empty = raw bytes / set = multipart</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Postman-style single-tab semantic instead of radio toggle</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>16.16</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Frontend: inline left-bar error message (no large banners)</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Postman-style subdued inline feedback</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>16.17</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>Frontend: project uploads library - collapsible tight rows with thumb/ext / check for active / hover-only delete</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Postman-style tight row list</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>16.18</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Frontend: Flow card surfaces "Refreshing access tokens..." banner during prereq phase</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Previously only a PREREQ pill switch - banner makes the wait self-explanatory</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>16.19</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Frontend: Audit button copy "Snapshot &amp; report" + tooltip clarifies no re-checks happen</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Button now reads as the action it performs</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>16.20</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Fix: x button on selected file now deletes from project (not just unbinds from step)</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>User reported: deleted file still appeared in Project uploads list</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Replace native window.confirm for upload delete with two-click inline confirm (matches existing step-delete pattern from 15.4)</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Stays in-app instead of jumping to browser modal</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>16.22</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Prereq banner now shows live step-N-of-M + completed count + retry chip + filling progress bar</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Previously opaque - users couldn't tell if prereq was progressing or stuck</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>16.23</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>FlowCard Run-now lifts prereq runId up so PrereqsPanel attaches and shows the full step-by-step progress UI (matching panel's own Run-now behaviour)</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>User feedback: panel's complete bar only appeared when prereq triggered from the panel itself</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Backend: copyFlowStepToFlow + moveFlowStepToFlow store fns (transactional / target positions shifted +1 / insert at pos=1 / source rebalanced on move)</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Single tx() per operation - no partial state on failure</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" t="inlineStr">
         <is>
           <t>17.2</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Backend: POST /api/steps/:id/copy-to-flow + /move-to-flow routes (400 on missing step / same flow / missing target)</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Reuses existing getFlow + getFlowStep guards</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Frontend: reorderPrereqSteps + copyStepToFlow + moveStepToFlow API wrappers</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Mirrors existing reorderFlowSteps pattern</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Frontend: utils/varRefs.ts helper - findVarRefs + checkStepVarRefs scans url/body/headers/query for {{name}} tokens</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Reusable across Flow steps + Prereq steps via union type</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Frontend: arrow-up/down micro-stack column on every step row (FlowCard + PrereqsPanel) with first/last disabled + optimistic UI + disabled mid-run</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Manager chose arrow buttons over drag-and-drop</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Frontend: hover-revealed Move + Copy buttons on Flow step rows (not prereqs) - opens MoveCopyStepModal</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>Scope is flow-to-flow only per design</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>17.7</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>Frontend: MoveCopyStepModal lists other flows in project / empty-state row / confirm-row with Move-arrow or Copy-arrow primary button</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Drop position is always step 1 of target (no position picker)</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Frontend: warn chip on rows with broken {{var}} refs after reorder (non-blocking - runtime still attempts and surfaces real error)</t>
         </is>
       </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Allow + warn per design - never blocks user</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Smoke test: copy + move + reorder routes verified via curl on Default project (positions rebalanced correctly on both sides)</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Edges tested: same-flow 400 / missing step 400 / missing targetFlowId 400</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Fix: Move/Copy target flow now auto-refreshes (ProjectView combines flowsTick into the refreshTick passed to FlowCards)</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>User-reported: target flow didn't update until manual reload</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>17.11</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>Fix: deleteFlowStep + deletePrereqStep rebalance positions inside tx() so 1/2/3 -&gt; 1/2 after deleting position 2</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>User-reported: numbers stayed sparse (1/3) after deletion</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>17.12</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Scroll position survives page reload via localStorage (fm:scroll:&lt;projectId&gt;) + beforeunload/pagehide/visibilitychange + double-rAF restore on first snapshot</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>User requested - was in-memory only before</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>17.13</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Per-project section memory: switching back to a project restores the last-viewed tab (#urls vs #flows) instead of forcing #urls; mirrored to localStorage on switch + page-hide</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>User-reported: switching projects was always resetting to #urls even on return visit</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Backend types.ts: new ForEachConfig interface + forEach field on FlowStep</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Single-level only - one for-each per flow</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>18.2</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Backend types.ts: iterationIndex + iterationCount on StepResult; forEachIteration + forEachTotal on LiveStepProgress</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Same iterationCount across every row of one iteration set</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>18.3</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Backend extraction.ts: jsonPath learns [*] wildcard (recursive flatten); ExtractedValue.value widened to string | unknown[]</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>$.data[*] returns whole array; $.data[*].id returns array of ids</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>18.4</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Backend extraction.ts: substitute learns dotted-path lookup (walks object-typed vars for {{student.id}})</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Bridges per-iteration item objects to template syntax</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>18.5</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Backend db.ts: idempotent ensureColumn migrations - for_each_config_json on flow_steps + iteration_index + iteration_count on step_results</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Existing rows default NULL = non-iterating step</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>18.6</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Backend store.ts: normalizeForEach (identifier validation) + assertSingleForEach (single-level guard) + serialize/parse in add/update/copy/move</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>400 with 'only one for-each step is allowed per flow' on guard violation</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Backend store.ts: recordStepResult writes iterationIndex/iterationCount; rowToFlowStep + rowToStepResult parse them back</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Prereq runner passes nulls (prereqs never iterate)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>18.8</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts: iteration fork - resolves array var / caps at 100 / loops with per-iteration vars / records per-iteration row / never stops flow on iter failure</t>
         </is>
       </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Failure policy locked by user constraint #1 - continue all iterations</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts: LiveStepProgress publishes forEachIteration + forEachTotal between iterations</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Mid-flight UI gets 'iteration X of N' label</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>18.10</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts + assertions.ts + prereqRunner.ts: widen vars map to Record&lt;string</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>unknown&gt; with stringify on persistence</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>Bridges array/object vars in-memory vs string-only DB rows</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>18.11</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Frontend types.ts: mirror backend - ForEachConfig + forEach on FlowStep + iteration* on StepResult + forEach* on LiveStepProgress</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Single source-of-truth alignment</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>18.12</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Frontend flowForms.tsx: new For each tab with dropdown of array-typed vars + item-name input + Disable button + single-level warning banner</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Candidates auto-derived from earlier steps' extractions that use [*]</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>18.13</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: arrow-cycle pill 'for each {{item}}' in step header next to method tag</t>
         </is>
       </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Indigo tint - subtle but discoverable</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>18.14</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: (N) check X / cross Y summary chip + chevron toggles scrollable per-iteration panel (status + latency + error reason + retry count)</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Max-height 260px - doesn't render 100 inline rows per user constraint #3</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>18.15</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: live progress label gets 'iteration X of N' suffix when liveStep.forEachTotal set</t>
         </is>
       </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Increments per iteration; complements existing Step N of M label</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>18.16</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Frontend varRefs.ts: regex widened to recognise {{name.dotted.path}}; checkStepVarRefs adds loop-local itemVarName to known set</t>
         </is>
       </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>No false-warn for {{student.id}} inside a for-each step</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>18.17</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Frontend styles.css: .step-foreach-pill (indigo) + .step-iterations-summary (green/red w/ chevron) + .step-iterations-panel + .step-foreach-warning (yellow)</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Visual weight matches existing extract-row editor</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" t="inlineStr">
         <is>
           <t>18.18</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>Build clean: tsc -b on backend + tsc -b + vite build on frontend</t>
         </is>
       </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Zero warnings; production bundle 273KB JS / 58KB CSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>18.1.1</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: parent DnD state + handleDropReorder with splice + offset math; optimistic UI + rollback on API failure</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Replaces handleReorder; insertAt = fromIdx&lt;toIdx ? toIdx-1 : toIdx</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>18.1.2</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx StepRow: replaced step-reorder arrows with step-grip (grip dots + position); row-level onDragOver computes above/below by cursor Y vs midpoint</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Only grip is draggable; rest of row stays click-to-edit + drop zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>18.1.3</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Frontend PrereqsPanel.tsx: mirrored same DnD treatment (handleDropReorder + PrereqStepRow grip + row handlers)</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Same code path as FlowCard; sharing styles</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>18.1.4</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: removed .step-reorder*; added .step-grip + .step-dragging + .step-drop-above/below (2px accent insertion line via pseudo-elements)</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>No layout shift; cursor grab -&gt; grabbing -&gt; not-allowed while running</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>18.1.5</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Drop indicator suppresses no-op hovers (dragging row N over its own above-line or row N-1 below-line)</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>UX polish - avoids misleading insertion line for identity drops</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>18.1.6</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Smoke test: POST /api/flows/:id/steps/reorder with swapped order verified against for-each demo flow on Default project</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Order swapped + restored cleanly via the same API DnD invokes</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>18.1.7</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Phase 1.18.1 - DnD step reorder</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Build clean: npx tsc -b + npx vite build zero warnings</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Bundle 275.60KB JS / 58.27KB CSS</t>
         </is>
       </c>
     </row>

--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6774,6 +6774,294 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>18.2.1</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Added @dnd-kit/core + @dnd-kit/sortable + @dnd-kit/utilities deps</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Bundle +52KB raw / +17KB gzip - industry standard, Linear/Notion/Vercel use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>18.2.2</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>New StepDragHandle.tsx exports GripIcon (SVG 2x3 dot grid) + StepDragPreview (floating overlay content)</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Shared between FlowCard + PrereqsPanel; SVG scales crisply at any DPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>18.2.3</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>FlowCard.tsx: SortedStepList wraps step list in DndContext + SortableContext + DragOverlay; StepRow uses useSortable({id})</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>verticalListSortingStrategy; closestCenter collision; 220ms cubic-bezier drop animation</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>18.2.4</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PrereqsPanel.tsx: mirrored - SortedPrereqStepList + PrereqStepRow.useSortable</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Identical UX across both panels</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>18.2.5</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Sensors: PointerSensor (distance:8) + KeyboardSensor (sortableKeyboardCoordinates) for full a11y</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Tab to grip, Space to grab, arrows to move, Space to drop, Esc to cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>18.2.6</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Drop handler uses arrayMove(sorted, fromIdx, toIdx); optimistic UI swap + rollback on reorder API failure</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Same /steps/reorder backend route as 1.18.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>18.2.7</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>styles.css: .step-grip focusable button w/ focus-ring + touch-action:none; .step-dragging 35% opacity; .step-drag-preview lifted shadow + 1.02 scale + -0.4 deg tilt + backdrop blur</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Production-grade visual polish</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>18.2.8</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Removed .step-drop-above/below pseudo-element insertion lines</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>dnd-kit slide-out-of-the-way animation makes drop position obvious without separate indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>18.2.9</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Phase 1.18.2 - dnd-kit production DnD</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Build clean: tsc + vite build zero warnings; bundle 327KB JS / 59KB CSS (gzip 96KB / 11KB)</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>No new TS warnings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$234</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,15 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009CA3AF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -39,21 +50,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="001F2937"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,17 +72,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,15 +478,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6588 +522,7485 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Backend project setup (Node.js + TypeScript + Express)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>tsx watch dev server</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Frontend project setup (React + Vite + TypeScript)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Vite dev server with proxy to backend</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Implement URL ingestion endpoint (POST /api/urls)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Add and remove URLs via REST</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Implement status checker (HTTP GET to URL)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Captures HTTP status code</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Group URLs by status family (2xx/3xx/4xx/5xx/error)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>classify() pure function</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Frontend dashboard with grouped count cards</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>React + CSS color-coded</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Real-time refresh (frontend polls every 3s)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>setInterval + useEffect</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Phase 1 - Foundations</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>JSON file persistence with atomic writes</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>data/db.json with .tmp + rename</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Project segregation (multiple projects + sidebar)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Each project = monitored service</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Per-project API key vault</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Configurable header name + prefix</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Auth header injection for monitored URLs</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Bearer / x-api-key / Basic supported</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Per-URL configurable check interval</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Default 5 min; range 1-1440</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>5-phase HTTP latency tracking</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>DNS / TCP / TLS / TTFB / Download via raw https</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Description field per URL</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Free-text endpoint label</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Error reason mapping (human-readable)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>DNS fail / cert expired / 401 / 503 etc</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Slack webhook integration for failure alerts</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Auto-fire on transition to failing</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Phase 1.5 - Production polish</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Latency bar visualization (per-check breakdown)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Color-coded segments per phase</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Modal/dialog system (replace browser prompts)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Reusable Modal + ConfirmDialog</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Toast notifications (success / error feedback)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Auto-dismiss after 3.5s</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Design token system (spacing / type / radius / motion)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>CSS custom properties</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Polished sidebar with project avatars + health dots</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Color-hashed initials</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Phase 1.6 - UX refresh</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Animated transitions and hover states</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Cards lift; modals slide-up</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Migrate from JSON file to SQLite (node:sqlite)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Built-in - no native compile</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Schema design (projects/keys/urls/checks tables)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Foreign keys + indexes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Auto-migrate existing db.json to SQLite</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Old file backed up as .migrated.bak</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Persistent check history (every check stored)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>checks table with timestamps</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>7-day retention policy with auto-pruning</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Hourly cleanup job</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Phase 1.7 - Storage upgrade</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Extend retention to 365 days for long-range views</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Was 7 days; now keeps a year</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Sparkline component (24h latency trend)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Pure SVG no library</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Status strip (24h commit-graph style)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Replaced by Activity Timeline (5.7)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Failure rate chip (color-coded by severity)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Green &lt;1% / Amber 1-5% / Red &gt;5%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>KPI bar (4 KPIs + project sparkline)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Total / Healthy% / Avg latency / Failing</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>/api/urls/:id/history endpoint</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Returns checks since timestamp</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>/api/urls/:id/stats endpoint</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Total / failures / avg / p99</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Activity Timeline (unified history viz)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Replaces status strip + sparkline</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Time Range Selector (24h/7d/30d/90d/1y/Custom) - LinkedIn style</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Re-renders all charts based on selection</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>5.10</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Time Range Selector visual redesign (segmented pill + sliding indicator)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Datadog/Linear-inspired premium look</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Skeleton loaders on first paint</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Shimmer placeholders before /api/status arrives</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>12.2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Spinner component + busy state in async buttons</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Replaces text-only Checking... state</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Toast notifications with success/error/info icons</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>SVG icons + colored borders</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Pulse animation on failing/degraded health dots in sidebar</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Calls attention to broken services</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Staggered fade+slide entrance for URL cards</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>40ms stagger between cards</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Smooth transitions on status pills + KPIs + chips</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>No more abrupt color/value snaps</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Consistent focus-visible rings across interactive elements</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Keyboard navigation accessibility</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Phase 1.12 - UX polish</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Reduced-motion media query (a11y)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Respects prefers-reduced-motion</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Backend: flows + flow_steps + flow_runs + step_results + variable_cache tables</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>SQLite schema with full FK relations</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>13.2</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Backend: extraction.ts with mini JSONPath + header + status capture</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Zero deps; supports $.foo.bar / arrays / quoted keys</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Backend: variable substitution ({{name}} in URL/headers/body/params)</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Find-and-replace before sending</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Backend: flowRunner.ts - atomic execution + stop-on-failure + skip cascade</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Industry standard atomic flow execution</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Backend: smart caching with TTL (skip step if all vars still fresh)</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Massive cost saver - don't re-login if token valid</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>13.6</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Backend: per-step retries with exponential backoff</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Kills false alerts from network blips</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Backend: custom wait between steps for async APIs</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>POST job -&gt; wait 5s -&gt; poll status</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>13.8</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Backend: monitor scheduler extended to run due flows atomically</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>One interval per flow not per step</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Backend: Slack alert on flow failure (per-project webhook)</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Reuses existing slack.ts</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>13.10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Backend: 13 REST endpoints (flows/steps/runs/cache CRUD)</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Full CRUD + reorder + manual trigger</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Frontend: FlowEditor modal (name/interval/stop-on-failure)</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Create + edit + enable/disable</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>13.12</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Frontend: StepEditor modal with 7 tabs (Basics/Params/Headers/Body/Assertions/Extract/Retry)</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Full Postman parity + extractions + retries</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>13.13</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Frontend: Variables hint shows available {{vars}} from prior steps</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Self-documenting flow editor</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>13.14</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Frontend: FlowCard with expandable step list + per-step results</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>One run shown inline; click step to edit</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>13.15</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Frontend: Run Now button with spinner + last-run timestamp</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Manual trigger from UI</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>13.16</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Frontend: Flows section integrated above Standalone URLs in ProjectView</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Clean separation of flows vs independent URLs</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>13.17</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UX: wrap Flows + URLs in visual section panels with header/count/actions</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Notion/Linear style - fixes orphaned search bar issue</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>13.18</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UX: GitHub-style tab navigation (Standalone URLs / Flows) with count badges + active underline</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Each tab has its own search/filters - scales to many items</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>13.19</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UX: URL hash persistence for tabs (#urls / #flows) + danger badge on failing count</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Refresh stays on same tab; bookmarkable; failures visible without switching</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>13.20</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UX: switching projects in sidebar resets to URLs tab (deep-link still respected on refresh)</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Fixes confusing "I was on Flows in A; clicking B opens Flows in B too"</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>13.21</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UX: tighten vertical rhythm (main gap 24px-&gt;12px) + breathing room before section panel</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Less visual clutter; rests where rests are needed</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>13.22</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Backend: Run Audit now includes flows (re-runs all enabled flows alongside URL checks)</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Single button audits everything in project</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>13.23</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Backend: HTML report has dedicated Flows table section + 4 KPIs with breakdown</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>URLs section + Flows section + per-step status badges</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>13.24</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Backend: Slack Block Kit message split into URL track + Flow track</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Dual stats row + separate failing lists for each type</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>13.25</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Backend: store extends list queries with lastRunOk + lastRunTotalMs via correlated subquery</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Single SQL roundtrip - no N+1 issue</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>13.26</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Frontend: KpiBar flow-aware (Endpoints label + breakdowns) with graceful no-flows fallback</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Single bar tells full story</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>13.27</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Frontend: Audit result modal shows dual-track URL/Flow breakdown</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Clear separation in result feedback</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>13.28</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Frontend: Flows tab gets mini-KPI strip (Total/Healthy/Failing/Avg run/Last run)</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Flow-level health at a glance</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>13.29</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UX: Flow KPI strip enlarged + tooltips on every cell + show which flow last ran</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Last run cell shows flow name as subtext; all cells hover-explained</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>13.30</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Phase 1.13 - Flows (API chaining)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Fix: Flow KPI strip auto-updates after Run Now (no page refresh needed)</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FlowCard onAfterRun callback bumps a flows-refresh tick in ProjectView</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Phase 1.8 - History UI</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Dynamic axis labels (hours/days/dates) based on window</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Activity Timeline auto-formats</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>HTTP method support (GET/POST/PUT/PATCH)</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>DELETE blocked for safety</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Body editor with type selector</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>JSON / form / urlencoded</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Custom headers tab (key-value editor)</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Sent on every check</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Query parameters tab (key-value editor)</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Appended to URL automatically</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Assertions engine (4 v1 types)</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>status equals / in range / latency under / body contains</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Assertion result pills on URL cards</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Green check / red X</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Phase 1.9 - Postman parity</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Raw body type with custom Content-Type (Text/XML/HTML/JS/YAML/custom)</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Postman raw mode equivalent</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Run Audit button (manual Check All)</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Concurrency capped at 8 parallel</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>HTML report generator</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Standalone HTML in data/reports/</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Slack Block Kit message format</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Rich KPIs and failure details</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Slack file upload (HTML attached)</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>@slack/web-api files.uploadV2</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Audit progress modal + result modal</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Spinner during run; summary after</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Phase 1.10 - Audit + Slack</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Get Slack Bot Token (xoxb-) and configure</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>User: paste in Settings to enable Slack uploads</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Search by URL/description/method</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Filters list live as you type</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Numbered pagination (LeetCode style)</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Smart ellipsis for many pages</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Method filter chips (color-coded)</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>GET green / POST orange / PUT cyan / PATCH purple</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Search bar with icon + keyboard shortcut (/)</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Press / anywhere to focus</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Result count chip in search</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Highlights blue when filter active</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Phase 1.11 - Discoverability</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>New URLs appear at top of list</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>ORDER BY rowid DESC</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Demo: API key with/without (httpbin/bearer)</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>Showed 401 vs 200 with same URL</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Demo: Basic Auth with httpbin/basic-auth</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>Different auth style demonstrated</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Demo: POST + JSON body to httpbin/post</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>Confirmed body sent correctly</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Explanation doc: how Phase 1 connects to Phase 2</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>Mapped each Phase 2 requirement to Phase 1 file</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Demo &amp; explanation</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Manager meeting: present plan and get approval</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>User to schedule</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>14.1</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Backend: 4 new tables (prereq_steps / prereq_runs / prereq_step_results / project_variable_cache) + project columns</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Project-level setup chain + variable pool</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Backend: store CRUD + run lifecycle + project-pool variable cache</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>listPrereqSteps / startPrereqRun / cacheProjectVariable etc.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Backend: prereqRunner.ts (sequential exec</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> retries</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> wait</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> TTL</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> captures to project pool)</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>Mirrors flowRunner with project-scoped persistence</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Backend: monitor.ts substitutes project-pool {{vars}} into every standalone URL check</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>URL custom headers and body now resolve {{auth_token}} etc.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Backend: flowRunner.ts merges project pool + flow cache (flow-scoped wins on conflict)</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Hierarchical variable scoping (project &lt; flow)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>14.6</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Backend: monitor tick auto-runs due prereq chains (before URLs/flows)</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tokens stay warm without manual refresh</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Backend: REST endpoints (CRUD prereq steps / run / list runs / get vars / clear vars)</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>7 new routes wired in index.ts</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>14.8</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Frontend: PrereqsPanel — collapsible panel above tab nav with status header + Run Now</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Visible on both URLs and Flows tabs</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Frontend: PrereqStepEditorForm (shares 7-tab UX with FlowStep editor)</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Reuses BodyEditor / AssertionsEditor / ExtractionsEditor / RetryWaitEditor</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>14.10</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Frontend: Variables hint in Flow step editor now includes prereq-chain vars</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Surfaced via projectVars prop loaded by App</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Frontend: live project variable list (with TTL countdown) + Clear vars button</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Renders captured pool inline in the panel</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>14.12</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Frontend: per-project schedule controls (interval + enable/disable)</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Saves via PATCH /projects/:id with new fields</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>14.13</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Smoke test: prereq captures token + URL substitutes it + body-contains assertion passes</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>End-to-end substitution proven via httpbin /post → /headers</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>14.14</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Backend: {{var}} substitution inside assertion config (body-contains text)</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Closes the brittleness gap — assertions tracking rotating session/auth tokens stay green</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>14.15</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Backend: evaluateAssertions accepts vars param + 3 callsites wire it through (monitor / flowRunner / prereqRunner)</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Single source of truth - same vars used for substitution everywhere</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>14.16</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Frontend: assertion UI hints {{var}} support (placeholder + tip line)</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Users discover the feature without docs</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>14.17</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Smoke test: prereq re-run after pool clear keeps flow green automatically</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Proven across 3 step shapes (body / header / query param) on Default project</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>14.18</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Backend: split runners into kickoff (sync runId) + executeRun (background); new /run-async endpoints return 202 with runId</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Frontend can now show live per-step progress instead of a blocking spinner</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>14.19</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Frontend: FlowCard + PrereqsPanel poll runId every 500ms; render running-pulse pill / queued dashed pill / progress bar</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Step state transitions queued &gt; running &gt; done in real time</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>14.20</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UX: progress bar shows 'Step N of M running...' + completed count above step list</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Replaces 'simply loading n loading' opaque spinner</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>14.21</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Backend: force flag on kickoff functions bypasses smart TTL skip-cache; /run-async accepts ?force=true</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Production-grade pattern - human clicks bypass caches</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> scheduler keeps them</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>14.22</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Frontend: manual Run-now buttons always pass force=true (FlowCard + PrereqsPanel)</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Button now does what it says - no more confusing SKIPPED on click</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>14.23</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Phase 1.14 - Prerequisites</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Smoke test: scheduler skips when fresh / manual click always refreshes the pool</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Verified pool value before/after to prove both paths</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Active project persists across page refresh (localStorage)</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Refresh keeps you where you were instead of dumping to default</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>15.2</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Per-project scroll memory: save on leave / restore on return / top on fresh</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Switching projects no longer 'inherits' middle-of-page scroll from the previous one</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Prereq panel auto-collapses 1.5s after run completes (restores pre-click state)</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Expands during run for live progress then snaps back as if untouched</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Two-click inline confirm for step delete (replaces native window.confirm)</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Avoids ugly browser confirm modal nested inside our editor modal</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>15.5</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>Document title reflects active project + failing count</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Tab title now '(3 failing) Project Name - Functional Monitor'</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>15.6</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Sidebar shows failing-count badge per project (pulsing red)</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Spot failing projects at a glance without clicking each one</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>Step rows truncate long URLs cleanly (ellipsis + monospace)</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Prevents long URLs from pushing the edit hint off the card</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Backend: liveStep map in flowRunner + prereqRunner; each retry attempt + backoff phase is published in-memory</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Enables live retry visibility without DB writes per attempt</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>15.9</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>Backend: GET /flow-runs/:id and /prereq-runs/:id enrich response with optional liveStep while run is mid-flight</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Single endpoint - existing poll cadence picks it up</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>15.10</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Frontend: running step pill switches to amber "RETRY N/M" + step row tints amber during retries</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Distinguishes a retry-in-progress from a fresh attempt</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>15.11</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>Frontend: progress bar shows "retry N of M (waiting before next try)" + last-try status code chip</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>No more silent waits during exponential backoff</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>15.12</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Phase 1.15 - UX hardening</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Smoke test: 503 endpoint with 3 retries traces attempt 1 to 4 transitions including backoff phase</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Verified via /api/flow-runs/:id polling at 350ms cadence</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>Backend: uploads table + on-disk storage in data/uploads/&lt;uuid&gt;</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>One row per file; bytes live on disk not in SQLite</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>Backend: paths.ts helper centralises UPLOADS_DIR + per-id path</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Shared by index.ts upload routes and timing.ts body builder</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>16.3</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>Backend: POST/GET/DELETE routes (express.raw 10MB cap; URL-encoded x-filename header)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>No multer dependency; raw bytes go straight to disk</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>16.4</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Backend: store CRUD (createUpload/getUpload/listUploadsByProject/deleteUpload)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Mirrors existing row-mapper pattern</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>Backend: bodyType=binary in timing.ts parses {uploadId fieldName?} body and builds raw or multipart</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Empty fieldName = raw bytes; set = multipart/form-data</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Frontend: shared BinaryBodyEditor with file picker / image preview / field-name / existing-uploads picker</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Single component reused by URL + Flow step + Prereq step editors</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>16.7</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Frontend: Binary tab added to all three body editors (URL form / Flow step / Prereq step)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Discoverable in same Body tab as JSON / Raw / form-data</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UX: Run Now on a Flow auto-runs the prereq chain first with force=true</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Avoids spurious failures from stale auth tokens</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UX: Audit renamed Generate report - snapshots current state; ?refresh=true opt-in for re-check</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Used to re-run everything; now defaults to fast snapshot</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Smoke test: upload list readback delete round-trip via curl</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Verified POST returns id; GET streams bytes; DELETE 204s</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>16.11</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Frontend: BinaryBodyEditor rebuilt in Postman style - Select File button + inline filename + clear x; compact utilitarian row</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>User feedback: oversized dropzone felt out of place vs rest of Postman-like editor</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>16.12</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Frontend: real upload progress bar (XHR onprogress with %) replaces opaque "Uploading..." text</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Live feedback for large files; no more guessing if it hung</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>16.13</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Frontend: client-side max-size guard (10MB) shows inline error before hitting server</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Saves a wasted upload + slow round-trip for over-cap files</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>16.14</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Frontend: inline filename + size display with x clear button (Postman binary tab layout)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Matches Postman binary body editor exactly</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>16.15</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>Frontend: Field name (optional) inline input - empty = raw bytes / set = multipart</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Postman-style single-tab semantic instead of radio toggle</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>16.16</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Frontend: inline left-bar error message (no large banners)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Postman-style subdued inline feedback</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>16.17</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Frontend: project uploads library - collapsible tight rows with thumb/ext / check for active / hover-only delete</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Postman-style tight row list</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>16.18</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Frontend: Flow card surfaces "Refreshing access tokens..." banner during prereq phase</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Previously only a PREREQ pill switch - banner makes the wait self-explanatory</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>16.19</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>Frontend: Audit button copy "Snapshot &amp; report" + tooltip clarifies no re-checks happen</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Button now reads as the action it performs</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>16.20</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>Fix: x button on selected file now deletes from project (not just unbinds from step)</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>User reported: deleted file still appeared in Project uploads list</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>Replace native window.confirm for upload delete with two-click inline confirm (matches existing step-delete pattern from 15.4)</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Stays in-app instead of jumping to browser modal</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>16.22</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>Prereq banner now shows live step-N-of-M + completed count + retry chip + filling progress bar</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Previously opaque - users couldn't tell if prereq was progressing or stuck</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>16.23</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Phase 1.16 - Binary uploads + UX tightening</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>FlowCard Run-now lifts prereq runId up so PrereqsPanel attaches and shows the full step-by-step progress UI (matching panel's own Run-now behaviour)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>User feedback: panel's complete bar only appeared when prereq triggered from the panel itself</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>Backend: copyFlowStepToFlow + moveFlowStepToFlow store fns (transactional / target positions shifted +1 / insert at pos=1 / source rebalanced on move)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Single tx() per operation - no partial state on failure</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>17.2</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>Backend: POST /api/steps/:id/copy-to-flow + /move-to-flow routes (400 on missing step / same flow / missing target)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Reuses existing getFlow + getFlowStep guards</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>Frontend: reorderPrereqSteps + copyStepToFlow + moveStepToFlow API wrappers</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Mirrors existing reorderFlowSteps pattern</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Frontend: utils/varRefs.ts helper - findVarRefs + checkStepVarRefs scans url/body/headers/query for {{name}} tokens</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Reusable across Flow steps + Prereq steps via union type</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Frontend: arrow-up/down micro-stack column on every step row (FlowCard + PrereqsPanel) with first/last disabled + optimistic UI + disabled mid-run</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Manager chose arrow buttons over drag-and-drop</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Frontend: hover-revealed Move + Copy buttons on Flow step rows (not prereqs) - opens MoveCopyStepModal</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Scope is flow-to-flow only per design</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>17.7</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Frontend: MoveCopyStepModal lists other flows in project / empty-state row / confirm-row with Move-arrow or Copy-arrow primary button</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Drop position is always step 1 of target (no position picker)</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Frontend: warn chip on rows with broken {{var}} refs after reorder (non-blocking - runtime still attempts and surfaces real error)</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Allow + warn per design - never blocks user</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Smoke test: copy + move + reorder routes verified via curl on Default project (positions rebalanced correctly on both sides)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Edges tested: same-flow 400 / missing step 400 / missing targetFlowId 400</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>Fix: Move/Copy target flow now auto-refreshes (ProjectView combines flowsTick into the refreshTick passed to FlowCards)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>User-reported: target flow didn't update until manual reload</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>17.11</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>Fix: deleteFlowStep + deletePrereqStep rebalance positions inside tx() so 1/2/3 -&gt; 1/2 after deleting position 2</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>User-reported: numbers stayed sparse (1/3) after deletion</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>17.12</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>Scroll position survives page reload via localStorage (fm:scroll:&lt;projectId&gt;) + beforeunload/pagehide/visibilitychange + double-rAF restore on first snapshot</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>User requested - was in-memory only before</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>17.13</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Phase 1.17 - Step orchestration</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Per-project section memory: switching back to a project restores the last-viewed tab (#urls vs #flows) instead of forcing #urls; mirrored to localStorage on switch + page-hide</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>User-reported: switching projects was always resetting to #urls even on return visit</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>Backend types.ts: new ForEachConfig interface + forEach field on FlowStep</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Single-level only - one for-each per flow</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>18.2</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>Backend types.ts: iterationIndex + iterationCount on StepResult; forEachIteration + forEachTotal on LiveStepProgress</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Same iterationCount across every row of one iteration set</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>18.3</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>Backend extraction.ts: jsonPath learns [*] wildcard (recursive flatten); ExtractedValue.value widened to string | unknown[]</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>$.data[*] returns whole array; $.data[*].id returns array of ids</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>18.4</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>Backend extraction.ts: substitute learns dotted-path lookup (walks object-typed vars for {{student.id}})</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Bridges per-iteration item objects to template syntax</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>18.5</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>Backend db.ts: idempotent ensureColumn migrations - for_each_config_json on flow_steps + iteration_index + iteration_count on step_results</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Existing rows default NULL = non-iterating step</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>18.6</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>Backend store.ts: normalizeForEach (identifier validation) + assertSingleForEach (single-level guard) + serialize/parse in add/update/copy/move</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>400 with 'only one for-each step is allowed per flow' on guard violation</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>Backend store.ts: recordStepResult writes iterationIndex/iterationCount; rowToFlowStep + rowToStepResult parse them back</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Prereq runner passes nulls (prereqs never iterate)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>18.8</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts: iteration fork - resolves array var / caps at 100 / loops with per-iteration vars / records per-iteration row / never stops flow on iter failure</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Failure policy locked by user constraint #1 - continue all iterations</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts: LiveStepProgress publishes forEachIteration + forEachTotal between iterations</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Mid-flight UI gets 'iteration X of N' label</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>18.10</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>Backend flowRunner.ts + assertions.ts + prereqRunner.ts: widen vars map to Record&lt;string</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>unknown&gt; with stringify on persistence</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Bridges array/object vars in-memory vs string-only DB rows</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>18.11</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>Frontend types.ts: mirror backend - ForEachConfig + forEach on FlowStep + iteration* on StepResult + forEach* on LiveStepProgress</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Single source-of-truth alignment</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>18.12</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>Frontend flowForms.tsx: new For each tab with dropdown of array-typed vars + item-name input + Disable button + single-level warning banner</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Candidates auto-derived from earlier steps' extractions that use [*]</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>18.13</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: arrow-cycle pill 'for each {{item}}' in step header next to method tag</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Indigo tint - subtle but discoverable</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>18.14</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: (N) check X / cross Y summary chip + chevron toggles scrollable per-iteration panel (status + latency + error reason + retry count)</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Max-height 260px - doesn't render 100 inline rows per user constraint #3</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>18.15</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: live progress label gets 'iteration X of N' suffix when liveStep.forEachTotal set</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Increments per iteration; complements existing Step N of M label</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>18.16</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>Frontend varRefs.ts: regex widened to recognise {{name.dotted.path}}; checkStepVarRefs adds loop-local itemVarName to known set</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>No false-warn for {{student.id}} inside a for-each step</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>18.17</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>Frontend styles.css: .step-foreach-pill (indigo) + .step-iterations-summary (green/red w/ chevron) + .step-iterations-panel + .step-foreach-warning (yellow)</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Visual weight matches existing extract-row editor</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>18.18</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18 - For-each step</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>Build clean: tsc -b on backend + tsc -b + vite build on frontend</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Zero warnings; production bundle 273KB JS / 58KB CSS</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>18.1.1</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx: parent DnD state + handleDropReorder with splice + offset math; optimistic UI + rollback on API failure</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Replaces handleReorder; insertAt = fromIdx&lt;toIdx ? toIdx-1 : toIdx</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>18.1.2</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>Frontend FlowCard.tsx StepRow: replaced step-reorder arrows with step-grip (grip dots + position); row-level onDragOver computes above/below by cursor Y vs midpoint</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Only grip is draggable; rest of row stays click-to-edit + drop zone</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>18.1.3</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>Frontend PrereqsPanel.tsx: mirrored same DnD treatment (handleDropReorder + PrereqStepRow grip + row handlers)</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Same code path as FlowCard; sharing styles</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>18.1.4</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>Frontend styles.css: removed .step-reorder*; added .step-grip + .step-dragging + .step-drop-above/below (2px accent insertion line via pseudo-elements)</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>No layout shift; cursor grab -&gt; grabbing -&gt; not-allowed while running</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>18.1.5</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>Drop indicator suppresses no-op hovers (dragging row N over its own above-line or row N-1 below-line)</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>UX polish - avoids misleading insertion line for identity drops</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>18.1.6</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>Smoke test: POST /api/flows/:id/steps/reorder with swapped order verified against for-each demo flow on Default project</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Order swapped + restored cleanly via the same API DnD invokes</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>18.1.7</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.1 - DnD step reorder</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>Build clean: npx tsc -b + npx vite build zero warnings</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Bundle 275.60KB JS / 58.27KB CSS</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>18.2.1</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>Added @dnd-kit/core + @dnd-kit/sortable + @dnd-kit/utilities deps</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Bundle +52KB raw / +17KB gzip - industry standard, Linear/Notion/Vercel use it</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>18.2.2</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>New StepDragHandle.tsx exports GripIcon (SVG 2x3 dot grid) + StepDragPreview (floating overlay content)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Shared between FlowCard + PrereqsPanel; SVG scales crisply at any DPR</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>18.2.3</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>FlowCard.tsx: SortedStepList wraps step list in DndContext + SortableContext + DragOverlay; StepRow uses useSortable({id})</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>verticalListSortingStrategy; closestCenter collision; 220ms cubic-bezier drop animation</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>18.2.4</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>PrereqsPanel.tsx: mirrored - SortedPrereqStepList + PrereqStepRow.useSortable</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Identical UX across both panels</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>18.2.5</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>Sensors: PointerSensor (distance:8) + KeyboardSensor (sortableKeyboardCoordinates) for full a11y</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Tab to grip, Space to grab, arrows to move, Space to drop, Esc to cancel</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>18.2.6</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>Drop handler uses arrayMove(sorted, fromIdx, toIdx); optimistic UI swap + rollback on reorder API failure</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Same /steps/reorder backend route as 1.18.1</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>18.2.7</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>styles.css: .step-grip focusable button w/ focus-ring + touch-action:none; .step-dragging 35% opacity; .step-drag-preview lifted shadow + 1.02 scale + -0.4 deg tilt + backdrop blur</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Production-grade visual polish</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>18.2.8</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>Removed .step-drop-above/below pseudo-element insertion lines</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>dnd-kit slide-out-of-the-way animation makes drop position obvious without separate indicator</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>18.2.9</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>Phase 1.18.2 - dnd-kit production DnD</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>Build clean: tsc + vite build zero warnings; bundle 327KB JS / 59KB CSS (gzip 96KB / 11KB)</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>No new TS warnings</t>
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Backend types.ts: ForEachConfig doc updated for dotted-path arrayVarName; StepResult.iterationPath + iterationPathCount</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Nested-iteration tracking columns mirrored across backend + frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Backend db.ts: idempotent migrations for iteration_path_json + iteration_path_count_json columns on step_results</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Pre-1.19 rows default NULL = depth-1 (legacy iteration_index/_count still readable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Backend extraction.ts: new Scope + ScopeStack types; substitute()/resolveVar() walk innermost-first so inner loops shadow outer scopes</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Existing callsites pass bare Scope (wrapped as [scope]) - zero breaking changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Backend store.ts: assertSingleForEach -&gt; assertForEachDepth (static scope-stack walk / 4-level cap) wired into add/update/copy/move</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>400 'for-each depth cannot exceed 4 (got N)' on guard violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Backend store.ts: normalizeForEach accepts dotted-path arrayVarName (student.subjects); recordStepResult + rowToStepResult persist/parse iteration_path* JSON columns</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Identifier regex widened from [a-zA-Z_][a-zA-Z0-9_]* to dotted variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: LiveStepProgress.forEachPath + forEachTotalPath; new TOTAL_CALL_CAP = 10_000 constant</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Per-level cap (100) unchanged; total cap protects against 100^4 = 100M blow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: top-level for -&gt; while driver; new computeAbsorbedBlock() walks contiguous for-each steps whose arrayVarName roots through an in-scope loop var (depth &lt;= 4)</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Implicit nesting via variable refs - user never picks a parent loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: new runForEachBlock() recursive runner - per-iteration ScopeStack push/pop / direct-child recursion / depth-1 keeps iteration_index/_count for back-compat</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Failure policy preserved - all iterations continue at every level</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: total-call-budget guard (TOTAL_CALL_CAP) emits 'Truncated: total call cap (10000) reached' sentinel row + short-circuits current branch</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Single ctx.totalCalls counter shared across sibling blocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>19.10</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Frontend types.ts: mirror backend - StepResult.iterationPath/iterationPathCount + LiveStepProgress.forEachPath/forEachTotalPath</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Single source-of-truth alignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>19.11</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Frontend varRefs.ts: checkStepVarRefs walks ALL earlier for-each steps - lexical scope-stack pushes/pops match the runner so nested {{student.id}} + {{subject.id}} + {{mark.id}} resolve w/o false-warn</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>No spurious warning chips in deeply nested steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Frontend flowForms.tsx: ForEachEditor rewritten - grouped &lt;optgroup&gt; dropdown (extracted vars vs outer-loop items) / depth badge (1..4 colored) / pre-filled student. text input for loop-item mode</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Manager UX constraint: zero parent-loop picker / zero tree drawing</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>19.13</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Frontend flowForms.tsx: combinatorial-call banner ('This step will run up to ~10000 times per flow run...') live-recomputed from computeForEachDepth</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Sets user expectations before they hit the truncation cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Frontend flowForms.tsx: removed the locked single-level guard (multi-loop now allowed); dropped the warning banner</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Replaces 'another step already has forEach' block</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: loop-pill gets depth-{1..4} class (teal/violet/amber/rose) + tooltip naming outer scope; live progress label shows full path ('iteration 3/10 -&gt; 7/12 -&gt; 2/8')</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Depth color helps spot nesting structure at a glance</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>19.16</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: new IterationTree component - chevron-expandable per-level breadcrumb / left-edge color stripe per depth / 16px indent / branch-level ok/fail aggregation / 'truncated at 10000' chip</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Replaces flat per-iteration panel when iterationPath rows present</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>19.17</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: computeForEachDepth helper mirrors backend's static scope-stack walk so the depth pill color stays in sync with the runner's actual nesting</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Single algo cloned in 3 places (backend assertForEachDepth + checkStepVarRefs + computeForEachDepth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>19.18</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: .step-foreach-pill.depth-{1..4} + .step-foreach-depth-badge + .step-foreach-estimate + .step-iter-tree/children/level-{1..4} + .step-iter-node.fail + .step-iter-breadcrumb</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Visual weight matches existing Phase 1.18 iteration styling</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>19.19</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19 - Nested for-each (up to 4 levels)</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Build clean: npx tsc -b on backend; npx tsc -b + npx vite build on frontend (zero warnings)</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Bundle 333KB JS / 62KB CSS (gzip 98KB / 11KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>19.1.1</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Backend types.ts: new StepResult.resolvedUrl (URL fetched after {{var}} substitution; null for sentinels)</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Lets the iteration tree show the actual fetched URL per leaf instead of just the un-substituted template</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>19.1.2</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Backend db.ts: idempotent ensureColumn migration for resolved_url TEXT on step_results + prereq_step_results</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Picks up automatically on next backend start</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>19.1.3</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Backend store.ts: row interfaces + rowToStepResult/rowToPrereqStepResult mappers + recordStepResult/recordPrereqStepResult writers (25-col / 21-col INSERTs)</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Persist + read symmetric across both flow and prereq tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>19.1.4</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Backend flowRunner.ts: success-path recordStepResult calls (per-iteration + non-iter) pass resolved.url; sentinel paths leave null</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Sentinels (truncated/missing-var/cache-skip/upstream-failed) intentionally null since no real fetch happened</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>19.1.5</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Backend prereqRunner.ts: success-path recordPrereqStepResult passes resolved.url; cache-skip + upstream-failed sentinels leave null</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors flowRunner symmetric treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>19.1.6</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Frontend types.ts: mirror backend StepResult.resolvedUrl</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Single field add</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>19.1.7</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx IterNodeView: render ownRow.resolvedUrl as monospace truncated line under iteration breadcrumb (full URL on hover)</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Pre-1.19.1 rows naturally show no URL line since resolvedUrl is null</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>19.1.8</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: new .step-iter-node &gt; .iter-url (monospace + muted + ellipsis-truncate + 28px left-pad to align under breadcrumb status row)</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Scoped to .step-iter-node so it doesn't bleed into other .iter-url usages</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>19.1.9</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.19.1 - Resolved URL per iteration row</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Build clean (backend + frontend tsc + vite); depth-2 demo re-run confirms 17/17 rows now carry resolved URL</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Bundle 333KB JS / 62KB CSS gzip 98KB / 11KB - identical to 19.19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:J234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7999,8 +7999,608 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Backend audit.ts: stripped options.refresh block + options parameter from runAuditAndDeliver; removed checkAllInProject + runFlow imports</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot/Report is now strictly read-only per manager mandate</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Backend index.ts: dropped req.query.refresh parsing from POST /api/projects/:id/audit</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Separates trigger vs report</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Backend index.ts: new POST /api/projects/:id/check-urls reuses checkAllInProject(id 8); returns {checked ok failed durationMs}</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Powers Button 1 (Check all now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Backend index.ts: new POST /api/projects/:id/check-all - prereqs first sequentially then URLs + flows in parallel; continues even if prereqs fail</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Powers Button 2 (Run full check); prereqs must run first since they capture tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Frontend api.ts: new checkAllUrls + checkEntireProject helpers with typed result interfaces</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors runAudit helper shape</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Frontend App.tsx: handleCheckAllUrls + handleCheckEntireProject mirroring handleRunAudit; busyCheckUrls / busyFullCheck per-project; toast summary on completion</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Disables buttons during in-flight to prevent double-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: Button 1 (Check all now) added inside .method-chips-row wrapper right of HTTP method chips</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Disabled when urls.length === 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: Button 2 (Run full check) added in .hero-actions to the LEFT of Snapshot &amp; report (now default styling)</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot demoted to secondary action</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: new .method-chips-row (flex row space-between wraps on narrow widths) + .check-all-urls-btn (no-shrink no-wrap)</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Chips bar + trigger share one line</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>20.10</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20 - Manual check buttons + read-only audit</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Build clean: backend tsc -b + frontend tsc -b + vite build zero warnings; bundle 336KB JS / 63KB CSS (gzip 100KB / 11KB)</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>20.1.1</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: new externalRunId prop + useEffect that attaches to a parent-orchestrated flow run via handleRun({runId skipPrereqs:true}) without re-kicking it off</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors existing PrereqsPanel externalRunId pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>20.1.2</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Frontend FlowCard.tsx: handleRun refactored to accept {runId? skipPrereqs?}; Run now button wrapped as () =&gt; handleRun() so MouseEvent isnt mistaken for opts</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Single polling path serves both self-triggered and parent-orchestrated runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>20.1.3</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: new orchestrator state (fullCheckBusy fullCheckPhase orchestratorFlowRunId) + runFullCheckOrchestrator() driving prereqs sequentially then URLs in parallel with flows one-at-a-time</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Replaces App.tsx single /check-all call with visible per-phase async flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>20.1.4</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: new FullCheckBanner sub-component - sticky top phase-aware (Refreshing prerequisites -&gt; Checking URLs + running flows -&gt; Running flow X of Y: name -&gt; Full check complete) with inline spinner</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>User always sees what phase is happening even when on a different tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>20.1.5</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: FlowsSectionPanel threads orchestratorFlowRunId to the matching FlowCard (matched by flowId); exactly one card shows live step-by-step</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Per-flow card attaches via externalRunId and surfaces full progress UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>20.1.6</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Frontend App.tsx: removed handleCheckEntireProject + busyFullCheck + checkEntireProject import; ProjectView receives onAfterFullCheck + onToast instead</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Single-shot /check-all endpoint no longer driven from the UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>20.1.7</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Frontend styles.css: new .full-check-banner (sticky top blue-&gt;violet gradient 6px blur fade-in keyframes lifted shadow) + .full-check-banner-icon/-body/-label/-detail</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Polished sticky banner keeps progress visible while scrolling</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>20.1.8</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Backend POST /api/projects/:id/check-all kept intact for non-interactive callers (scripts/cron) but no longer the UIs path</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>UI now drives the same work through visible per-phase async endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>20.1.9</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.20.1 - Run full check live progress orchestration</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Build clean: backend tsc -b + frontend tsc -b + vite build zero warnings; bundle 339KB JS / 64KB CSS (gzip 100KB / 11KB)</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J234"/>
+  <autoFilter ref="A1:J253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C314"/>
+  <dimension ref="A1:C317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5292,7 +5292,7 @@
     <row r="293" ht="24" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01   -   17 tasks</t>
+          <t>2026-06-01   -   20 tasks</t>
         </is>
       </c>
       <c r="B293" s="3" t="n"/>
@@ -5301,8 +5301,8 @@
     <row r="294" ht="42" customHeight="1">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>Added a pure Loop step, live loop progress, and a new 'concat arrays' transform.
-Loop step declares 'repeat for each item' without a fake API call (~88 fewer calls per run). Loops show a live progress bar instead of 'QUEUED'. Compute step can now merge two lists (e.g. countries + regions) into one combined list to Loop together.</t>
+          <t>Added a pure Loop step, live loop progress, a 'concat arrays' transform, and the per-item version of it.
+Loop = repeat without a fake API call (~88 fewer calls per run). Live loop progress bar. 'Concat arrays' merges two lists. New: 'add a merged-list field to every item' — for each campaign, merge that campaign's countries + regions into one list and Loop it. Dogfooded on the real Logitech flow.</t>
         </is>
       </c>
       <c r="B294" s="3" t="n"/>
@@ -5597,44 +5597,95 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="24" customHeight="1">
-      <c r="A312" s="8" t="inlineStr">
+    <row r="312" ht="48" customHeight="1">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>22.3.1</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>Backend: 'merge lists per item' now actually works (the inner transform can see the item).</t>
+        </is>
+      </c>
+      <c r="C312" s="7" t="inlineStr">
+        <is>
+          <t>When the Compute step runs 'for each campaign, add a merged list of its countries + regions', the merge step needs to read fields off the CURRENT campaign. Backend now hands the current campaign into the inner step so it can find 'countries' and 'regions' on it. Older inner transforms (split text, slice, etc.) are unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="48" customHeight="1">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>22.3.2</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t>Frontend: 'merge lists' is now selectable as the inner step + has its own input boxes.</t>
+        </is>
+      </c>
+      <c r="C313" s="7" t="inlineStr">
+        <is>
+          <t>Two small fixes: (a) the inner-step dropdown was filtering out 'merge lists' — un-filtered it; (b) when you pick it, the editor now shows the same 'Source list 1 / Source list 2 / + Add another list' inputs as the top-level version, plus a short explainer note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="48" customHeight="1">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>22.3.3</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>Rewrote the live Logitech flow to use the new per-item merge (real dogfood).</t>
+        </is>
+      </c>
+      <c r="C314" s="7" t="inlineStr">
+        <is>
+          <t>Step 2 used to derive the locale via 'split text take part 0'; now Step 2 derives 'campaign.geos = countries + regions' per campaign. Step 4 iterates campaign.geos with the new URL format /campaign/{{documentId}}/{{locale}}/{{geo}}/discover. Result: 66/69 calls green; remaining 3 are real backend signal (zh-Hant locale 403s) — exactly what monitoring is for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="24" customHeight="1">
+      <c r="A315" s="8" t="inlineStr">
         <is>
           <t>Pending (no date yet)</t>
         </is>
       </c>
-      <c r="B312" s="3" t="n"/>
-      <c r="C312" s="3" t="n"/>
-    </row>
-    <row r="313" ht="28" customHeight="1">
-      <c r="A313" s="5" t="inlineStr">
+      <c r="B315" s="3" t="n"/>
+      <c r="C315" s="3" t="n"/>
+    </row>
+    <row r="316" ht="28" customHeight="1">
+      <c r="A316" s="5" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B313" s="6" t="inlineStr">
+      <c r="B316" s="6" t="inlineStr">
         <is>
           <t>Pending: get a Slack bot token (xoxb-) and paste it in Settings.</t>
         </is>
       </c>
-      <c r="C313" s="7" t="inlineStr">
+      <c r="C316" s="7" t="inlineStr">
         <is>
           <t>Enables the Slack file upload feature.</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="28" customHeight="1">
-      <c r="A314" s="5" t="inlineStr">
+    <row r="317" ht="28" customHeight="1">
+      <c r="A317" s="5" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B314" s="6" t="inlineStr">
+      <c r="B317" s="6" t="inlineStr">
         <is>
           <t>Pending: schedule a manager meeting to present the plan and get approval.</t>
         </is>
       </c>
-      <c r="C314" s="7" t="inlineStr">
+      <c r="C317" s="7" t="inlineStr">
         <is>
           <t>User to schedule.</t>
         </is>
@@ -5658,7 +5709,6 @@
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A269:C269"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A312:C312"/>
     <mergeCell ref="A156:C156"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A72:C72"/>
@@ -5674,6 +5724,7 @@
     <mergeCell ref="A270:C270"/>
     <mergeCell ref="A178:C178"/>
     <mergeCell ref="A281:C281"/>
+    <mergeCell ref="A315:C315"/>
     <mergeCell ref="A87:C87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C317"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5649,50 +5649,189 @@
       </c>
     </row>
     <row r="315" ht="24" customHeight="1">
-      <c r="A315" s="8" t="inlineStr">
-        <is>
-          <t>Pending (no date yet)</t>
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02   -   7 tasks</t>
         </is>
       </c>
       <c r="B315" s="3" t="n"/>
       <c r="C315" s="3" t="n"/>
     </row>
-    <row r="316" ht="28" customHeight="1">
-      <c r="A316" s="5" t="inlineStr">
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>Final UX sharpening — small polish all over the dashboard.
+Latencies show as '1.2s' instead of '1234ms'. Timestamps show as '3 min ago' instead of 'Jun 1, 2026, 3:45 PM'. Disabled buttons explain why. A toast appears if the backend connection drops (and another when it comes back). Bundle barely changed — 0.23 KB.</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="n"/>
+      <c r="C316" s="3" t="n"/>
+    </row>
+    <row r="317" ht="48" customHeight="1">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>22.4.1</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t>Built two shared formatters: 'how long' and 'how long ago'.</t>
+        </is>
+      </c>
+      <c r="C317" s="7" t="inlineStr">
+        <is>
+          <t>One reusable helper file. 'How long' turns 1234ms into 1.2s, 65000ms into 1m 5s. 'How long ago' turns a timestamp into 'just now' / '5 min ago' / '3h ago' / '12d ago'. Used everywhere from now on instead of each component rolling its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="48" customHeight="1">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>22.4.2</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>Replaced raw 'ms' numbers in 9 places across the dashboard.</t>
+        </is>
+      </c>
+      <c r="C318" s="7" t="inlineStr">
+        <is>
+          <t>Before: '1234ms'. After: '1.2s'. Touched the latency bar, flow cards, prereq panel, KPI cards, activity timeline tooltip, sparkline axis. Each one still shows the exact ms on hover for power users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="48" customHeight="1">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>22.4.3</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
+        <is>
+          <t>Replaced 4 'last run' / 'last check' timestamps with relative time.</t>
+        </is>
+      </c>
+      <c r="C319" s="7" t="inlineStr">
+        <is>
+          <t>Before: 'Jun 1, 2026, 3:45:22 PM'. After: '3 min ago'. Hover shows the full timestamp. Also deleted two near-duplicate helpers that two components had each written separately — single source of truth now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="48" customHeight="1">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>22.4.4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
+        <is>
+          <t>Disabled buttons now explain WHY they're disabled.</t>
+        </is>
+      </c>
+      <c r="C320" s="7" t="inlineStr">
+        <is>
+          <t>Before: hover a greyed 'Run now' button — no clue why it won't fire. After: tooltip says exactly why ('Add a step first' vs 'Flow is already running' vs 'Add a URL first'). Also added a proper screen-reader label to the bare-emoji 🗑 delete button (was being read as just 'wastebasket').</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="48" customHeight="1">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>22.4.5</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
+        <is>
+          <t>Dashboard now tells you when the backend connection drops.</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="inlineStr">
+        <is>
+          <t>Before: if the backend crashed, the page just froze on old data — no warning. After: one toast on disconnect ('Lost connection to the backend — showing stale data until it returns') and one toast when it comes back ('Reconnected to the server'). Won't spam — only fires on the change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="48" customHeight="1">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>22.4.6</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>Verified that the loop progress bar styling was already fine.</t>
+        </is>
+      </c>
+      <c r="C322" s="7" t="inlineStr">
+        <is>
+          <t>The audit flagged it as missing — but the CSS was already there at line 3791. No change needed; logged for honesty so the missing diff isn't confused for a missed item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="48" customHeight="1">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>22.4.7</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
+        <is>
+          <t>Clean build — bundle barely changed.</t>
+        </is>
+      </c>
+      <c r="C323" s="7" t="inlineStr">
+        <is>
+          <t>Frontend tsc + vite build both zero errors. Bundle: 361.27 KB JS (+0.23 KB from before), CSS unchanged. Tiny cost for measurable feel improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="8" t="inlineStr">
+        <is>
+          <t>Pending (no date yet)</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="n"/>
+      <c r="C324" s="3" t="n"/>
+    </row>
+    <row r="325" ht="28" customHeight="1">
+      <c r="A325" s="5" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B316" s="6" t="inlineStr">
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>Pending: get a Slack bot token (xoxb-) and paste it in Settings.</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
+      <c r="C325" s="7" t="inlineStr">
         <is>
           <t>Enables the Slack file upload feature.</t>
         </is>
       </c>
     </row>
-    <row r="317" ht="28" customHeight="1">
-      <c r="A317" s="5" t="inlineStr">
+    <row r="326" ht="28" customHeight="1">
+      <c r="A326" s="5" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B317" s="6" t="inlineStr">
+      <c r="B326" s="6" t="inlineStr">
         <is>
           <t>Pending: schedule a manager meeting to present the plan and get approval.</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
+      <c r="C326" s="7" t="inlineStr">
         <is>
           <t>User to schedule.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="35">
+    <mergeCell ref="A316:C316"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A149:C149"/>
     <mergeCell ref="A214:C214"/>
@@ -5709,6 +5848,7 @@
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A269:C269"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A324:C324"/>
     <mergeCell ref="A156:C156"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A72:C72"/>

--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$308</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J301"/>
+  <dimension ref="A1:J308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10138,8 +10138,232 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Backend openapiExport.ts (new): pure transform buildOpenAPISpec(project, urls, flows, prereqs); helpers - splitServerAndPath (URL() with {{var}} placeholder protection) + toOpenAPIPathKey ({{a.b}}-&gt;{a_b} so dotted vars stay distinct) + templateVarsToPathParams + extractServers (filters compute://step + loop://step sentinels) + buildSecuritySchemes (Authorization+Bearer -&gt; type:http scheme:bearer; else type:apiKey in:header name:headerName) + buildOperationForUrl/FlowStep/Prereq + mergeOperation (collision-safe path+method append with #id-slice alias key) + buildXMonFlow (full side-band with stepType+level+forEach+compute) + sortKeys (deterministic alphabetical paths); zero DB access</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Pure transform - no side effects testable in isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Backend index.ts: new GET /api/projects/:id/export/openapi?format=yaml|json (defaults YAML); reuses getProject + listUrlsByProject + listFlowsByProject + getFlowWithSteps + listPrereqSteps; emits via js-yaml dump (lineWidth 120 noRefs true sortKeys false) or JSON.stringify(spec,null,2); content-disposition attachment filename=&lt;slug&gt;-openapi.&lt;ext&gt; triggers browser download</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Mirrors existing report-download endpoint pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Backend package.json: added js-yaml@^4.1.0 + @types/js-yaml@^4.0.9; same lib will handle import parsing later picked once for round-trip symmetry</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>One dep covers both directions</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Frontend api.ts: new exportProjectOpenAPI(projectId,format) returning {blob,filename}; parses content-disposition for server-suggested filename falls back to openapi.&lt;ext&gt;</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Same fetch pattern as audit-report download</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Frontend ProjectView.tsx: new 📥 Export to Swagger button in hero-actions between Snapshot and settings icons; handler creates Blob URL triggers temp anchor download revokes URL pushes success/error toast; loading state Spinner + Exporting...; disabled when zero URLs AND zero flows with explanatory tooltip</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Standard browser download UX no new dep</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end smoke on live CMS/Logitech project: YAML export clean OpenAPI 3.0.3 - servers exactly the 2 real hosts (compute/loop sentinels filtered) + paths alphabetically sorted + /api/getCampaigns and 2 dotted-path-distinct /campaign/{campaign_documentId}/{campaign_locale}/{geo}/... paths + securitySchemes.campaign-api-key={type:http scheme:bearer} correctly derived from Bearer ApiKey + x-mon-flows round-trips Compute mapAddField-&gt;concatArrays(countries,regions) + Loop forEach{campaigns as campaign} + sibling L2 children with forEach{campaign.geos as geo} and full assertions+extractions+level+position; JSON variant parses cleanly; determinism verified (two consecutive exports byte-identical); Default project (no flows 12 hosts) also renders OK</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Full data-model round-trip via standard format</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.24 - Export to Swagger/OpenAPI</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Build clean: backend tsc -b zero output; frontend tsc -b zero output</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid encoding preserves all our orchestration metadata in x-mon-* extensions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J301"/>
+  <autoFilter ref="A1:J308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project-tracker.xlsx
+++ b/project-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$1:$J$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J308"/>
+  <dimension ref="A1:J316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10362,8 +10362,264 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Backend deps: removed @slack/web-api (22 packages); added nodemailer@^6.10.1 + @types/nodemailer@^6.4.17 devdep</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Webhook path was enough - bot-token UX was friction not feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Backend email.ts (new): mirrors slack.ts surface - sendUrlFailureEmail(project,url) + sendFlowFailureEmail(flow,run,project,failedStep) + sendAuditEmail({...with reportPath+reportFilename}) returning {sent,reason}; lazy getTransport() singleton reads SMTP_HOST/PORT/USER/PASS env once returns null if unset (graceful disable); parseRecipients splits on , ; \n; each sender bails early on empty recipients OR null transport; try/catch around sendMail logs+returns reason never throws so SMTP failure cannot crash a check; audit case adds attachments:[{filename,path,contentType:text/html}]</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Same fire-and-forget contract slack.ts has had for months</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Backend types.ts: Project drops slackBotToken+slackChannel adds notificationEmails:string; db.ts ensureColumn(projects, notification_emails, TEXT NOT NULL DEFAULT ''); store.ts ProjectRow drops slack_bot_token/slack_channel adds notification_emails + rowToProject reads it + createProject INSERT skips legacy columns (DEFAULT '' covers them) + updateProject patch keys updated; index.ts POST /api/projects body destructure updated</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Additive migration; legacy columns left dormant - dropping needs SQLite table-rebuild not worth the risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Backend slack.ts collapsed to webhook-only: removed WebClient import + entire sendAuditViaBot func (~170 lines incl Block Kit builders + files.uploadV2) + bot-token branch in sendAuditToSlack; sendAuditToSlack now returns no-creds reason if webhook empty else delegates to sendAuditViaWebhook (unchanged); URL+flow webhook senders unchanged</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>File shrunk ~60%; @slack/web-api removed safely</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>Parallel triggers via Promise.allSettled - monitor.ts doCheck (URL OK-&gt;FAIL transition site): wraps sendSlackAlert + sendUrlFailureEmail; flowRunner.ts executeRun (flow-failure site): wraps sendFlowFailureAlert + sendFlowFailureEmail with failedStep lookup; audit.ts runAuditAndDeliver: wraps sendAuditToSlack + sendAuditEmail and surfaces both via AuditResult.slack and AuditResult.email; one channel's failure can never suppress the other</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Independent channel gates - email-only/Slack-only/both/neither all valid per project</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>backend/.env.example (new): SMTP_HOST/PORT/USER/PASS/FROM template with Gmail SMTP defaults + App Password instructions + note that swapping to Logitech SMTP later = change 4 env vars no code change</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Demo-ready with Gmail; one-line swap to corporate SMTP later</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Frontend mirror: types.ts Project drops slackBotToken+slackChannel adds notificationEmails:string; api.ts updateProject Partial&lt;Pick&lt;...&gt;&gt; updated; forms.tsx SettingsForm replaces two Slack-bot inputs (token + channel) with one multi-line email textarea + helper line (comma/semicolon/newline separated, SMTP env requirement); ProjectView.tsx replaces tri-state chip with two independent chips - 🔔 Slack on (when webhook set) + 📧 Email on (when emails set) + 🔕 Notifications off (only when both empty)</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Settings modal loses 2 fields gains 1; chip cluster now per-channel visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1.25 - Email notifications + Slack bot-token removal</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>E2E smoke: backend tsc -b zero output + frontend tsc -b zero output; backend boot triggers migration (notification_emails column appears); GET /api/projects returns notificationEmails and no longer returns slackBotToken/slackChannel (3 existing projects load fine with '' default); PATCH /api/projects/:id with notificationEmails round-trips; POST /api/projects/:id/audit returns {slack,email} with email={sent:false,reason:'SMTP not configured'} when env absent (graceful degradation confirmed); Phase 1.24 OpenAPI export unaffected (HTTP 200 63KB)</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>No SMTP configured = silent no-op; real delivery validated when user adds Gmail app password to .env</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J308"/>
+  <autoFilter ref="A1:J316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>